--- a/WAYTHAI-FORYOU_Template.xlsx
+++ b/WAYTHAI-FORYOU_Template.xlsx
@@ -497,10 +497,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="115" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,76 +526,59 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>① ออเดอร์  — งานที่รับมาแต่ละงาน: ใส่ ชื่อลูกค้า+เบอร์โทร, ราคารวม, มัดจำที่รับมา → ระบบจะคำนวณ 'ยอดค้างรับ' = ราคารวม − มัดจำ ให้เอง</t>
+          <t>① ออเดอร์  — งานแต่ละงาน: ชื่อลูกค้า+เบอร์, ราคารวม, ต้นทุนรวม, มัดจำ → ระบบคิด 'ยอดค้างรับ'=ราคา−มัดจำ และ 'กำไร'=ราคา−ต้นทุน ให้เอง</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">             (1 แถว = 1 ออเดอร์ ระบบจะสร้างลูกค้า+งาน+ใบแจ้งหนี้ให้อัตโนมัติ)</t>
+          <t xml:space="preserve">          ★ 'แหล่งผลิต' (production_type): self = ผลิตเอง | outsourced = ส่งซัพพลายเออร์ผลิต</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>② รายจ่าย  — ค่าใช้จ่ายทุกอย่าง: ค่าไม้/ค่าสี = หมวด paint,wood ; ค่าโฆษณา = ads ; ขายออนไลน์ = marketing ; ค่าเช่า = rent</t>
+          <t xml:space="preserve">          ★ ถ้าออเดอร์เดียวมีทั้งผลิตเองและสั่งซัพ ให้แยกเป็น 2 แถว (รหัสต่างกัน) เช่น ORD1-A (self) / ORD1-B (outsourced)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>③ เงินสด   — เงินเข้า-ออกจริงในบัญชี (รับมัดจำ/รับชำระ = in ; จ่ายซัพ/เงินเดือน = out) ใช้คู่กับชีต②</t>
+          <t>② รายจ่าย  — ค่าใช้จ่ายทั่วไปที่ไม่ผูกกับออเดอร์: ค่าเช่า=rent, โฆษณา=ads, ขายออนไลน์=marketing ฯลฯ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>④ พนักงาน  — ช่างไม้/ช่างสี ใส่ กลุ่มงาน=production (เข้าต้นทุนผลิต) ; คนขายออนไลน์ ใส่ marketing (เข้าค่าการตลาด)</t>
+          <t>③ เงินสด   — เงินเข้า-ออกจริงในบัญชี (รับมัดจำ/ชำระ=in, จ่ายซัพ/เงินเดือน=out)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>④ พนักงาน  — ช่างไม้/ช่างสี=production, คนขายออนไลน์=marketing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>กติกาการกรอก:</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• แถว1=ชื่อไทย  แถว2=ชื่อฟิลด์ระบบ (ห้ามแก้)  เริ่มกรอกแถว3</t>
+          <t>กติกา: แถว1=ชื่อไทย แถว2=ชื่อฟิลด์ (ห้ามแก้) เริ่มกรอกแถว3 · ช่อง*สีเหลือง=จำเป็น · เงิน=บาท · วันที่=ปปปป-ดด-วว · ช่องมีลูกศร=เลือกจากรายการ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• ช่อง * และสีเหลือง = จำเป็น   • เงิน=บาท   • วันที่=ปปปป-ดด-วว (เช่น 2026-06-04)   • ช่องมีลูกศร=เลือกจากรายการ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>• 'รหัส' ห้ามซ้ำในชีตเดียวกัน</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>นำเข้า: เปิดเว็บ → แท็บ 'นำเข้าข้อมูล' → อัปโหลดไฟล์นี้ (อ่านทุกชีตอัตโนมัติ ยิงซ้ำไม่เบิ้ลข้อมูล)</t>
+          <t>นำเข้า: เว็บ → แท็บ 'นำเข้าข้อมูล' → อัปโหลดไฟล์นี้ (อ่านทุกชีตอัตโนมัติ ยิงซ้ำไม่เบิ้ล)</t>
         </is>
       </c>
     </row>
@@ -611,19 +594,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -644,7 +629,7 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>รายละเอียดงาน/ประเภท</t>
+          <t>รายละเอียดงาน</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
@@ -654,25 +639,35 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>แหล่งผลิต*</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>วันที่รับงาน*</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>วันนัดส่ง</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>ราคารวม (บาท)*</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>ต้นทุนรวม (บาท)</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>มัดจำ (บาท)</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>สถานะงาน</t>
         </is>
@@ -706,25 +701,35 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
+          <t>production_type</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
           <t>issue_date</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>due_date</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>total_price</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>total_cost</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>deposit</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -737,10 +742,12 @@
       <c r="D3" s="8" t="n"/>
       <c r="E3" s="8" t="n"/>
       <c r="F3" s="7" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="8" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="7" t="n"/>
       <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n"/>
@@ -749,10 +756,12 @@
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="8" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="8" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="7" t="n"/>
       <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -761,10 +770,12 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="8" t="n"/>
       <c r="F5" s="7" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="8" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -773,10 +784,12 @@
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="7" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="8" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="7" t="n"/>
       <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -785,10 +798,12 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="8" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="7" t="n"/>
       <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -797,10 +812,12 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="7" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="8" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="7" t="n"/>
       <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -809,10 +826,12 @@
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="7" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="8" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="7" t="n"/>
       <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -821,10 +840,12 @@
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="7" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="8" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="7" t="n"/>
       <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -833,10 +854,12 @@
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="7" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="8" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="7" t="n"/>
       <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -845,10 +868,12 @@
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="8" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="7" t="n"/>
       <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -857,10 +882,12 @@
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="8" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="7" t="n"/>
       <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -869,10 +896,12 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="7" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="8" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="7" t="n"/>
       <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -881,10 +910,12 @@
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="7" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="8" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="7" t="n"/>
       <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -893,10 +924,12 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="8" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="7" t="n"/>
       <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -905,10 +938,12 @@
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="7" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="8" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="7" t="n"/>
       <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
@@ -917,10 +952,12 @@
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="7" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="8" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="7" t="n"/>
       <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -929,10 +966,12 @@
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="7" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="8" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="7" t="n"/>
       <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
@@ -941,10 +980,12 @@
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="7" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="8" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="7" t="n"/>
       <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -953,10 +994,12 @@
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="8" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="7" t="n"/>
       <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
@@ -965,10 +1008,12 @@
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="8" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="7" t="n"/>
       <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -977,10 +1022,12 @@
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="7" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="8" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="7" t="n"/>
       <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -989,10 +1036,12 @@
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="7" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="8" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="7" t="n"/>
       <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -1001,10 +1050,12 @@
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="7" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="8" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="7" t="n"/>
       <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+      <c r="L25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -1013,10 +1064,12 @@
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="7" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="8" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="7" t="n"/>
       <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
@@ -1025,10 +1078,12 @@
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="7" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="8" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="7" t="n"/>
       <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
@@ -1037,10 +1092,12 @@
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="7" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="8" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="7" t="n"/>
       <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -1049,10 +1106,12 @@
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="7" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="8" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="7" t="n"/>
       <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -1061,10 +1120,12 @@
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="7" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="8" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="7" t="n"/>
       <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
@@ -1073,10 +1134,12 @@
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="7" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="8" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="7" t="n"/>
       <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -1085,10 +1148,12 @@
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="7" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="8" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="7" t="n"/>
       <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -1097,10 +1162,12 @@
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="7" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="8" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="7" t="n"/>
       <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+      <c r="L33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -1109,10 +1176,12 @@
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="7" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="8" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="7" t="n"/>
       <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -1121,10 +1190,12 @@
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="7" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="8" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="7" t="n"/>
       <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
+      <c r="L35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -1133,10 +1204,12 @@
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="7" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="8" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="7" t="n"/>
       <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -1145,10 +1218,12 @@
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="7" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="8" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="7" t="n"/>
       <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -1157,10 +1232,12 @@
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="7" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="8" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="7" t="n"/>
       <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
@@ -1169,10 +1246,12 @@
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="7" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="7" t="n"/>
-      <c r="I39" s="8" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="7" t="n"/>
       <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -1181,10 +1260,12 @@
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="7" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="8" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="7" t="n"/>
       <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -1193,10 +1274,12 @@
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="7" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="8" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="7" t="n"/>
       <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+      <c r="L41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
@@ -1205,10 +1288,12 @@
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="7" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="7" t="n"/>
-      <c r="I42" s="8" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="7" t="n"/>
       <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+      <c r="L42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
@@ -1217,10 +1302,12 @@
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="7" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="8" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="7" t="n"/>
       <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
@@ -1229,10 +1316,12 @@
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="7" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="8" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="7" t="n"/>
       <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
@@ -1241,10 +1330,12 @@
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="7" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="8" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="7" t="n"/>
       <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
+      <c r="L45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
@@ -1253,10 +1344,12 @@
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="7" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="8" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="7" t="n"/>
       <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+      <c r="L46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -1265,10 +1358,12 @@
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="7" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="8" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="7" t="n"/>
       <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
+      <c r="L47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -1277,10 +1372,12 @@
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="7" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="8" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="7" t="n"/>
       <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
@@ -1289,10 +1386,12 @@
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="7" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="8" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="7" t="n"/>
       <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
@@ -1301,10 +1400,12 @@
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="7" t="n"/>
-      <c r="G50" s="8" t="n"/>
-      <c r="H50" s="7" t="n"/>
-      <c r="I50" s="8" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="7" t="n"/>
       <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
@@ -1313,10 +1414,12 @@
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="7" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="8" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="7" t="n"/>
       <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
@@ -1325,10 +1428,12 @@
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="7" t="n"/>
-      <c r="G52" s="8" t="n"/>
-      <c r="H52" s="7" t="n"/>
-      <c r="I52" s="8" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="7" t="n"/>
       <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -1337,10 +1442,12 @@
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="7" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="7" t="n"/>
-      <c r="I53" s="8" t="n"/>
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="7" t="n"/>
       <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
@@ -1349,10 +1456,12 @@
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="7" t="n"/>
-      <c r="G54" s="8" t="n"/>
-      <c r="H54" s="7" t="n"/>
-      <c r="I54" s="8" t="n"/>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="7" t="n"/>
       <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
@@ -1361,10 +1470,12 @@
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="7" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="8" t="n"/>
+      <c r="G55" s="7" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="7" t="n"/>
       <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
@@ -1373,10 +1484,12 @@
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="7" t="n"/>
-      <c r="G56" s="8" t="n"/>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="8" t="n"/>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="7" t="n"/>
       <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
@@ -1385,10 +1498,12 @@
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="7" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="7" t="n"/>
-      <c r="I57" s="8" t="n"/>
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="7" t="n"/>
       <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
@@ -1397,10 +1512,12 @@
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="7" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="7" t="n"/>
-      <c r="I58" s="8" t="n"/>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="7" t="n"/>
       <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
+      <c r="L58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
@@ -1409,10 +1526,12 @@
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="7" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="8" t="n"/>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="7" t="n"/>
       <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
+      <c r="L59" s="8" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
@@ -1421,10 +1540,12 @@
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="7" t="n"/>
-      <c r="G60" s="8" t="n"/>
-      <c r="H60" s="7" t="n"/>
-      <c r="I60" s="8" t="n"/>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="7" t="n"/>
       <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
+      <c r="L60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
@@ -1433,10 +1554,12 @@
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="7" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="8" t="n"/>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="7" t="n"/>
       <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
+      <c r="L61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -1445,10 +1568,12 @@
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="7" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="8" t="n"/>
+      <c r="G62" s="7" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="7" t="n"/>
       <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
@@ -1457,10 +1582,12 @@
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="7" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="7" t="n"/>
-      <c r="I63" s="8" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="7" t="n"/>
       <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+      <c r="L63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -1469,10 +1596,12 @@
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="7" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="8" t="n"/>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="7" t="n"/>
       <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+      <c r="L64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -1481,10 +1610,12 @@
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="7" t="n"/>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="7" t="n"/>
-      <c r="I65" s="8" t="n"/>
+      <c r="G65" s="7" t="n"/>
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="7" t="n"/>
       <c r="J65" s="8" t="n"/>
+      <c r="K65" s="8" t="n"/>
+      <c r="L65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -1493,10 +1624,12 @@
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="7" t="n"/>
-      <c r="G66" s="8" t="n"/>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="8" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="7" t="n"/>
       <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
@@ -1505,10 +1638,12 @@
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="7" t="n"/>
-      <c r="G67" s="8" t="n"/>
-      <c r="H67" s="7" t="n"/>
-      <c r="I67" s="8" t="n"/>
+      <c r="G67" s="7" t="n"/>
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="7" t="n"/>
       <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+      <c r="L67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -1517,10 +1652,12 @@
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="7" t="n"/>
-      <c r="G68" s="8" t="n"/>
-      <c r="H68" s="7" t="n"/>
-      <c r="I68" s="8" t="n"/>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="7" t="n"/>
       <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+      <c r="L68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
@@ -1529,10 +1666,12 @@
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="7" t="n"/>
-      <c r="G69" s="8" t="n"/>
-      <c r="H69" s="7" t="n"/>
-      <c r="I69" s="8" t="n"/>
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="7" t="n"/>
       <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -1541,10 +1680,12 @@
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="7" t="n"/>
-      <c r="G70" s="8" t="n"/>
-      <c r="H70" s="7" t="n"/>
-      <c r="I70" s="8" t="n"/>
+      <c r="G70" s="7" t="n"/>
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="7" t="n"/>
       <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
+      <c r="L70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
@@ -1553,10 +1694,12 @@
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="7" t="n"/>
-      <c r="G71" s="8" t="n"/>
-      <c r="H71" s="7" t="n"/>
-      <c r="I71" s="8" t="n"/>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="7" t="n"/>
       <c r="J71" s="8" t="n"/>
+      <c r="K71" s="8" t="n"/>
+      <c r="L71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -1565,10 +1708,12 @@
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="7" t="n"/>
-      <c r="G72" s="8" t="n"/>
-      <c r="H72" s="7" t="n"/>
-      <c r="I72" s="8" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="7" t="n"/>
       <c r="J72" s="8" t="n"/>
+      <c r="K72" s="8" t="n"/>
+      <c r="L72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
@@ -1577,10 +1722,12 @@
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="7" t="n"/>
-      <c r="G73" s="8" t="n"/>
-      <c r="H73" s="7" t="n"/>
-      <c r="I73" s="8" t="n"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="7" t="n"/>
       <c r="J73" s="8" t="n"/>
+      <c r="K73" s="8" t="n"/>
+      <c r="L73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -1589,10 +1736,12 @@
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="7" t="n"/>
-      <c r="G74" s="8" t="n"/>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="8" t="n"/>
+      <c r="G74" s="7" t="n"/>
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="7" t="n"/>
       <c r="J74" s="8" t="n"/>
+      <c r="K74" s="8" t="n"/>
+      <c r="L74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
@@ -1601,10 +1750,12 @@
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="7" t="n"/>
-      <c r="G75" s="8" t="n"/>
-      <c r="H75" s="7" t="n"/>
-      <c r="I75" s="8" t="n"/>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="7" t="n"/>
       <c r="J75" s="8" t="n"/>
+      <c r="K75" s="8" t="n"/>
+      <c r="L75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -1613,10 +1764,12 @@
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="7" t="n"/>
-      <c r="G76" s="8" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="8" t="n"/>
+      <c r="G76" s="7" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="7" t="n"/>
       <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+      <c r="L76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
@@ -1625,10 +1778,12 @@
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="7" t="n"/>
-      <c r="G77" s="8" t="n"/>
-      <c r="H77" s="7" t="n"/>
-      <c r="I77" s="8" t="n"/>
+      <c r="G77" s="7" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="7" t="n"/>
       <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -1637,10 +1792,12 @@
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="7" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="7" t="n"/>
-      <c r="I78" s="8" t="n"/>
+      <c r="G78" s="7" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="7" t="n"/>
       <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
+      <c r="L78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
@@ -1649,10 +1806,12 @@
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="7" t="n"/>
-      <c r="G79" s="8" t="n"/>
-      <c r="H79" s="7" t="n"/>
-      <c r="I79" s="8" t="n"/>
+      <c r="G79" s="7" t="n"/>
+      <c r="H79" s="8" t="n"/>
+      <c r="I79" s="7" t="n"/>
       <c r="J79" s="8" t="n"/>
+      <c r="K79" s="8" t="n"/>
+      <c r="L79" s="8" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -1661,10 +1820,12 @@
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="7" t="n"/>
-      <c r="G80" s="8" t="n"/>
-      <c r="H80" s="7" t="n"/>
-      <c r="I80" s="8" t="n"/>
+      <c r="G80" s="7" t="n"/>
+      <c r="H80" s="8" t="n"/>
+      <c r="I80" s="7" t="n"/>
       <c r="J80" s="8" t="n"/>
+      <c r="K80" s="8" t="n"/>
+      <c r="L80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
@@ -1673,10 +1834,12 @@
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="7" t="n"/>
-      <c r="G81" s="8" t="n"/>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="8" t="n"/>
+      <c r="G81" s="7" t="n"/>
+      <c r="H81" s="8" t="n"/>
+      <c r="I81" s="7" t="n"/>
       <c r="J81" s="8" t="n"/>
+      <c r="K81" s="8" t="n"/>
+      <c r="L81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -1685,10 +1848,12 @@
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="7" t="n"/>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="7" t="n"/>
-      <c r="I82" s="8" t="n"/>
+      <c r="G82" s="7" t="n"/>
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="7" t="n"/>
       <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
+      <c r="L82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
@@ -1697,10 +1862,12 @@
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="7" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="7" t="n"/>
-      <c r="I83" s="8" t="n"/>
+      <c r="G83" s="7" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="7" t="n"/>
       <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
+      <c r="L83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -1709,10 +1876,12 @@
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="7" t="n"/>
-      <c r="G84" s="8" t="n"/>
-      <c r="H84" s="7" t="n"/>
-      <c r="I84" s="8" t="n"/>
+      <c r="G84" s="7" t="n"/>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="7" t="n"/>
       <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
+      <c r="L84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n"/>
@@ -1721,10 +1890,12 @@
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="7" t="n"/>
-      <c r="G85" s="8" t="n"/>
-      <c r="H85" s="7" t="n"/>
-      <c r="I85" s="8" t="n"/>
+      <c r="G85" s="7" t="n"/>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="7" t="n"/>
       <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
+      <c r="L85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -1733,10 +1904,12 @@
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="7" t="n"/>
-      <c r="G86" s="8" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="8" t="n"/>
+      <c r="G86" s="7" t="n"/>
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="7" t="n"/>
       <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
+      <c r="L86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
@@ -1745,10 +1918,12 @@
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="7" t="n"/>
-      <c r="G87" s="8" t="n"/>
-      <c r="H87" s="7" t="n"/>
-      <c r="I87" s="8" t="n"/>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="8" t="n"/>
+      <c r="I87" s="7" t="n"/>
       <c r="J87" s="8" t="n"/>
+      <c r="K87" s="8" t="n"/>
+      <c r="L87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -1757,10 +1932,12 @@
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="7" t="n"/>
-      <c r="G88" s="8" t="n"/>
-      <c r="H88" s="7" t="n"/>
-      <c r="I88" s="8" t="n"/>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="7" t="n"/>
       <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -1769,10 +1946,12 @@
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="7" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="7" t="n"/>
-      <c r="I89" s="8" t="n"/>
+      <c r="G89" s="7" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="7" t="n"/>
       <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -1781,10 +1960,12 @@
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="7" t="n"/>
-      <c r="G90" s="8" t="n"/>
-      <c r="H90" s="7" t="n"/>
-      <c r="I90" s="8" t="n"/>
+      <c r="G90" s="7" t="n"/>
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="7" t="n"/>
       <c r="J90" s="8" t="n"/>
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -1793,10 +1974,12 @@
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="7" t="n"/>
-      <c r="G91" s="8" t="n"/>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="8" t="n"/>
+      <c r="G91" s="7" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="7" t="n"/>
       <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -1805,10 +1988,12 @@
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="7" t="n"/>
-      <c r="G92" s="8" t="n"/>
-      <c r="H92" s="7" t="n"/>
-      <c r="I92" s="8" t="n"/>
+      <c r="G92" s="7" t="n"/>
+      <c r="H92" s="8" t="n"/>
+      <c r="I92" s="7" t="n"/>
       <c r="J92" s="8" t="n"/>
+      <c r="K92" s="8" t="n"/>
+      <c r="L92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -1817,10 +2002,12 @@
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="7" t="n"/>
-      <c r="G93" s="8" t="n"/>
-      <c r="H93" s="7" t="n"/>
-      <c r="I93" s="8" t="n"/>
+      <c r="G93" s="7" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="7" t="n"/>
       <c r="J93" s="8" t="n"/>
+      <c r="K93" s="8" t="n"/>
+      <c r="L93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -1829,10 +2016,12 @@
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="8" t="n"/>
       <c r="F94" s="7" t="n"/>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="7" t="n"/>
-      <c r="I94" s="8" t="n"/>
+      <c r="G94" s="7" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="7" t="n"/>
       <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
+      <c r="L94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -1841,10 +2030,12 @@
       <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="7" t="n"/>
-      <c r="G95" s="8" t="n"/>
-      <c r="H95" s="7" t="n"/>
-      <c r="I95" s="8" t="n"/>
+      <c r="G95" s="7" t="n"/>
+      <c r="H95" s="8" t="n"/>
+      <c r="I95" s="7" t="n"/>
       <c r="J95" s="8" t="n"/>
+      <c r="K95" s="8" t="n"/>
+      <c r="L95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -1853,10 +2044,12 @@
       <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="7" t="n"/>
-      <c r="G96" s="8" t="n"/>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="8" t="n"/>
+      <c r="G96" s="7" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="7" t="n"/>
       <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -1865,10 +2058,12 @@
       <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="7" t="n"/>
-      <c r="G97" s="8" t="n"/>
-      <c r="H97" s="7" t="n"/>
-      <c r="I97" s="8" t="n"/>
+      <c r="G97" s="7" t="n"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="7" t="n"/>
       <c r="J97" s="8" t="n"/>
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -1877,10 +2072,12 @@
       <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="7" t="n"/>
-      <c r="G98" s="8" t="n"/>
-      <c r="H98" s="7" t="n"/>
-      <c r="I98" s="8" t="n"/>
+      <c r="G98" s="7" t="n"/>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="7" t="n"/>
       <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
+      <c r="L98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -1889,10 +2086,12 @@
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="7" t="n"/>
-      <c r="G99" s="8" t="n"/>
-      <c r="H99" s="7" t="n"/>
-      <c r="I99" s="8" t="n"/>
+      <c r="G99" s="7" t="n"/>
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="7" t="n"/>
       <c r="J99" s="8" t="n"/>
+      <c r="K99" s="8" t="n"/>
+      <c r="L99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -1901,14 +2100,19 @@
       <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="7" t="n"/>
-      <c r="G100" s="8" t="n"/>
-      <c r="H100" s="7" t="n"/>
-      <c r="I100" s="8" t="n"/>
+      <c r="G100" s="7" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="7" t="n"/>
       <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
+      <c r="L100" s="8" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="J3:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="F3:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"self,outsourced"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"quote,in_progress,done,delivered"</formula1>
     </dataValidation>
   </dataValidations>

--- a/WAYTHAI-FORYOU_Template.xlsx
+++ b/WAYTHAI-FORYOU_Template.xlsx
@@ -497,10 +497,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="125" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>กรอกแค่ 4 ชีตนี้พอ (ดูแท็บด้านล่าง):</t>
+          <t>กรอกแค่ 4 ชีตนี้พอ:</t>
         </is>
       </c>
     </row>
@@ -526,59 +526,66 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>① ออเดอร์  — งานแต่ละงาน: ชื่อลูกค้า+เบอร์, ราคารวม, ต้นทุนรวม, มัดจำ → ระบบคิด 'ยอดค้างรับ'=ราคา−มัดจำ และ 'กำไร'=ราคา−ต้นทุน ให้เอง</t>
+          <t>① ออเดอร์  — งานแต่ละงาน: ชื่อลูกค้า+เบอร์, ราคารวม, แล้วแยกต้นทุน 'ค่าไม้/ค่าสี/ค่าแรง/ค่าส่ง', มัดจำ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">          ★ 'แหล่งผลิต' (production_type): self = ผลิตเอง | outsourced = ส่งซัพพลายเออร์ผลิต</t>
+          <t xml:space="preserve">          ★ ระบบจะรวมต้นทุน = ไม้+สี+แรง+ส่ง เอง → คำนวณกำไรของงาน และดึง 'ค่าสี' ไปโชว์บน Dashboard ให้</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">          ★ ถ้าออเดอร์เดียวมีทั้งผลิตเองและสั่งซัพ ให้แยกเป็น 2 แถว (รหัสต่างกัน) เช่น ORD1-A (self) / ORD1-B (outsourced)</t>
+          <t xml:space="preserve">          ★ แหล่งผลิต: self=ผลิตเอง | outsourced=สั่งซัพ (กรณีสั่งซัพ ใส่ยอดจ่ายซัพในช่อง 'ค่าไม้')</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>② รายจ่าย  — ค่าใช้จ่ายทั่วไปที่ไม่ผูกกับออเดอร์: ค่าเช่า=rent, โฆษณา=ads, ขายออนไลน์=marketing ฯลฯ</t>
+          <t xml:space="preserve">          ★ ออเดอร์เดียวมีทั้งผลิตเอง+สั่งซัพ → แยกเป็น 2 แถว (รหัสต่างกัน)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>③ เงินสด   — เงินเข้า-ออกจริงในบัญชี (รับมัดจำ/ชำระ=in, จ่ายซัพ/เงินเดือน=out)</t>
+          <t>② รายจ่าย  — ค่าใช้จ่ายที่ไม่ผูกกับออเดอร์: ค่าเช่า=rent, โฆษณา=ads, ขายออนไลน์=marketing (อย่าใส่ค่าไม้/สีซ้ำที่นี่ถ้าใส่ในออเดอร์แล้ว)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>③ เงินสด   — เงินเข้า-ออกจริงในบัญชี (รับมัดจำ/ชำระ=in, จ่ายซัพ/เงินเดือน=out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>④ พนักงาน  — ช่างไม้/ช่างสี=production, คนขายออนไลน์=marketing</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>กติกา: แถว1=ชื่อไทย แถว2=ชื่อฟิลด์ (ห้ามแก้) เริ่มกรอกแถว3 · ช่อง*สีเหลือง=จำเป็น · เงิน=บาท · วันที่=ปปปป-ดด-วว · ช่องมีลูกศร=เลือกจากรายการ</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>นำเข้า: เว็บ → แท็บ 'นำเข้าข้อมูล' → อัปโหลดไฟล์นี้ (อ่านทุกชีตอัตโนมัติ ยิงซ้ำไม่เบิ้ล)</t>
+          <t>กติกา: แถว1=ชื่อไทย แถว2=ชื่อฟิลด์(ห้ามแก้) เริ่มกรอกแถว3 · ช่อง*สีเหลือง=จำเป็น · เงิน=บาท · วันที่=ปปปป-ดด-วว · ช่องมีลูกศร=เลือกจากรายการ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>นำเข้า: เว็บ → แท็บ 'นำเข้าข้อมูล' → อัปโหลดไฟล์นี้ (ยิงซ้ำไม่เบิ้ล)</t>
         </is>
       </c>
     </row>
@@ -594,21 +601,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -659,15 +669,30 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>ต้นทุนรวม (บาท)</t>
+          <t>ค่าไม้ (บาท)</t>
         </is>
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
+          <t>ค่าสี (บาท)</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>ค่าแรง (บาท)</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>ค่าส่ง (บาท)</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
           <t>มัดจำ (บาท)</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>สถานะงาน</t>
         </is>
@@ -721,15 +746,30 @@
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>total_cost</t>
+          <t>cost_wood</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
+          <t>cost_paint</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>cost_labor</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>cost_shipping</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
           <t>deposit</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -748,6 +788,9 @@
       <c r="J3" s="8" t="n"/>
       <c r="K3" s="8" t="n"/>
       <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n"/>
@@ -762,6 +805,9 @@
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n"/>
       <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="8" t="n"/>
+      <c r="O4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -776,6 +822,9 @@
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="8" t="n"/>
       <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -790,6 +839,9 @@
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -804,6 +856,9 @@
       <c r="J7" s="8" t="n"/>
       <c r="K7" s="8" t="n"/>
       <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -818,6 +873,9 @@
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -832,6 +890,9 @@
       <c r="J9" s="8" t="n"/>
       <c r="K9" s="8" t="n"/>
       <c r="L9" s="8" t="n"/>
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -846,6 +907,9 @@
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -860,6 +924,9 @@
       <c r="J11" s="8" t="n"/>
       <c r="K11" s="8" t="n"/>
       <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -874,6 +941,9 @@
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -888,6 +958,9 @@
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -902,6 +975,9 @@
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -916,6 +992,9 @@
       <c r="J15" s="8" t="n"/>
       <c r="K15" s="8" t="n"/>
       <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -930,6 +1009,9 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -944,6 +1026,9 @@
       <c r="J17" s="8" t="n"/>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
@@ -958,6 +1043,9 @@
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -972,6 +1060,9 @@
       <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
@@ -986,6 +1077,9 @@
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -1000,6 +1094,9 @@
       <c r="J21" s="8" t="n"/>
       <c r="K21" s="8" t="n"/>
       <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
@@ -1014,6 +1111,9 @@
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -1028,6 +1128,9 @@
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -1042,6 +1145,9 @@
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -1056,6 +1162,9 @@
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
+      <c r="M25" s="8" t="n"/>
+      <c r="N25" s="8" t="n"/>
+      <c r="O25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -1070,6 +1179,9 @@
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="8" t="n"/>
+      <c r="O26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
@@ -1084,6 +1196,9 @@
       <c r="J27" s="8" t="n"/>
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="8" t="n"/>
+      <c r="M27" s="8" t="n"/>
+      <c r="N27" s="8" t="n"/>
+      <c r="O27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
@@ -1098,6 +1213,9 @@
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -1112,6 +1230,9 @@
       <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n"/>
       <c r="L29" s="8" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="8" t="n"/>
+      <c r="O29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -1126,6 +1247,9 @@
       <c r="J30" s="8" t="n"/>
       <c r="K30" s="8" t="n"/>
       <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="8" t="n"/>
+      <c r="O30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
@@ -1140,6 +1264,9 @@
       <c r="J31" s="8" t="n"/>
       <c r="K31" s="8" t="n"/>
       <c r="L31" s="8" t="n"/>
+      <c r="M31" s="8" t="n"/>
+      <c r="N31" s="8" t="n"/>
+      <c r="O31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -1154,6 +1281,9 @@
       <c r="J32" s="8" t="n"/>
       <c r="K32" s="8" t="n"/>
       <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -1168,6 +1298,9 @@
       <c r="J33" s="8" t="n"/>
       <c r="K33" s="8" t="n"/>
       <c r="L33" s="8" t="n"/>
+      <c r="M33" s="8" t="n"/>
+      <c r="N33" s="8" t="n"/>
+      <c r="O33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -1182,6 +1315,9 @@
       <c r="J34" s="8" t="n"/>
       <c r="K34" s="8" t="n"/>
       <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
+      <c r="O34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -1196,6 +1332,9 @@
       <c r="J35" s="8" t="n"/>
       <c r="K35" s="8" t="n"/>
       <c r="L35" s="8" t="n"/>
+      <c r="M35" s="8" t="n"/>
+      <c r="N35" s="8" t="n"/>
+      <c r="O35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -1210,6 +1349,9 @@
       <c r="J36" s="8" t="n"/>
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="8" t="n"/>
+      <c r="O36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -1224,6 +1366,9 @@
       <c r="J37" s="8" t="n"/>
       <c r="K37" s="8" t="n"/>
       <c r="L37" s="8" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="8" t="n"/>
+      <c r="O37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -1238,6 +1383,9 @@
       <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
       <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="8" t="n"/>
+      <c r="O38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
@@ -1252,6 +1400,9 @@
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
       <c r="L39" s="8" t="n"/>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="8" t="n"/>
+      <c r="O39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -1266,6 +1417,9 @@
       <c r="J40" s="8" t="n"/>
       <c r="K40" s="8" t="n"/>
       <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -1280,6 +1434,9 @@
       <c r="J41" s="8" t="n"/>
       <c r="K41" s="8" t="n"/>
       <c r="L41" s="8" t="n"/>
+      <c r="M41" s="8" t="n"/>
+      <c r="N41" s="8" t="n"/>
+      <c r="O41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
@@ -1294,6 +1451,9 @@
       <c r="J42" s="8" t="n"/>
       <c r="K42" s="8" t="n"/>
       <c r="L42" s="8" t="n"/>
+      <c r="M42" s="8" t="n"/>
+      <c r="N42" s="8" t="n"/>
+      <c r="O42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
@@ -1308,6 +1468,9 @@
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="8" t="n"/>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
@@ -1322,6 +1485,9 @@
       <c r="J44" s="8" t="n"/>
       <c r="K44" s="8" t="n"/>
       <c r="L44" s="8" t="n"/>
+      <c r="M44" s="8" t="n"/>
+      <c r="N44" s="8" t="n"/>
+      <c r="O44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
@@ -1336,6 +1502,9 @@
       <c r="J45" s="8" t="n"/>
       <c r="K45" s="8" t="n"/>
       <c r="L45" s="8" t="n"/>
+      <c r="M45" s="8" t="n"/>
+      <c r="N45" s="8" t="n"/>
+      <c r="O45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
@@ -1350,6 +1519,9 @@
       <c r="J46" s="8" t="n"/>
       <c r="K46" s="8" t="n"/>
       <c r="L46" s="8" t="n"/>
+      <c r="M46" s="8" t="n"/>
+      <c r="N46" s="8" t="n"/>
+      <c r="O46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -1364,6 +1536,9 @@
       <c r="J47" s="8" t="n"/>
       <c r="K47" s="8" t="n"/>
       <c r="L47" s="8" t="n"/>
+      <c r="M47" s="8" t="n"/>
+      <c r="N47" s="8" t="n"/>
+      <c r="O47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -1378,6 +1553,9 @@
       <c r="J48" s="8" t="n"/>
       <c r="K48" s="8" t="n"/>
       <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
@@ -1392,6 +1570,9 @@
       <c r="J49" s="8" t="n"/>
       <c r="K49" s="8" t="n"/>
       <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
@@ -1406,6 +1587,9 @@
       <c r="J50" s="8" t="n"/>
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="8" t="n"/>
+      <c r="M50" s="8" t="n"/>
+      <c r="N50" s="8" t="n"/>
+      <c r="O50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
@@ -1420,6 +1604,9 @@
       <c r="J51" s="8" t="n"/>
       <c r="K51" s="8" t="n"/>
       <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
+      <c r="N51" s="8" t="n"/>
+      <c r="O51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
@@ -1434,6 +1621,9 @@
       <c r="J52" s="8" t="n"/>
       <c r="K52" s="8" t="n"/>
       <c r="L52" s="8" t="n"/>
+      <c r="M52" s="8" t="n"/>
+      <c r="N52" s="8" t="n"/>
+      <c r="O52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -1448,6 +1638,9 @@
       <c r="J53" s="8" t="n"/>
       <c r="K53" s="8" t="n"/>
       <c r="L53" s="8" t="n"/>
+      <c r="M53" s="8" t="n"/>
+      <c r="N53" s="8" t="n"/>
+      <c r="O53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
@@ -1462,6 +1655,9 @@
       <c r="J54" s="8" t="n"/>
       <c r="K54" s="8" t="n"/>
       <c r="L54" s="8" t="n"/>
+      <c r="M54" s="8" t="n"/>
+      <c r="N54" s="8" t="n"/>
+      <c r="O54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
@@ -1476,6 +1672,9 @@
       <c r="J55" s="8" t="n"/>
       <c r="K55" s="8" t="n"/>
       <c r="L55" s="8" t="n"/>
+      <c r="M55" s="8" t="n"/>
+      <c r="N55" s="8" t="n"/>
+      <c r="O55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
@@ -1490,6 +1689,9 @@
       <c r="J56" s="8" t="n"/>
       <c r="K56" s="8" t="n"/>
       <c r="L56" s="8" t="n"/>
+      <c r="M56" s="8" t="n"/>
+      <c r="N56" s="8" t="n"/>
+      <c r="O56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
@@ -1504,6 +1706,9 @@
       <c r="J57" s="8" t="n"/>
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="8" t="n"/>
+      <c r="M57" s="8" t="n"/>
+      <c r="N57" s="8" t="n"/>
+      <c r="O57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
@@ -1518,6 +1723,9 @@
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="8" t="n"/>
       <c r="L58" s="8" t="n"/>
+      <c r="M58" s="8" t="n"/>
+      <c r="N58" s="8" t="n"/>
+      <c r="O58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
@@ -1532,6 +1740,9 @@
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
+      <c r="M59" s="8" t="n"/>
+      <c r="N59" s="8" t="n"/>
+      <c r="O59" s="8" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
@@ -1546,6 +1757,9 @@
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
+      <c r="M60" s="8" t="n"/>
+      <c r="N60" s="8" t="n"/>
+      <c r="O60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
@@ -1560,6 +1774,9 @@
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
+      <c r="M61" s="8" t="n"/>
+      <c r="N61" s="8" t="n"/>
+      <c r="O61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -1574,6 +1791,9 @@
       <c r="J62" s="8" t="n"/>
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
+      <c r="M62" s="8" t="n"/>
+      <c r="N62" s="8" t="n"/>
+      <c r="O62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
@@ -1588,6 +1808,9 @@
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
+      <c r="M63" s="8" t="n"/>
+      <c r="N63" s="8" t="n"/>
+      <c r="O63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -1602,6 +1825,9 @@
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
+      <c r="M64" s="8" t="n"/>
+      <c r="N64" s="8" t="n"/>
+      <c r="O64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -1616,6 +1842,9 @@
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
       <c r="L65" s="8" t="n"/>
+      <c r="M65" s="8" t="n"/>
+      <c r="N65" s="8" t="n"/>
+      <c r="O65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -1630,6 +1859,9 @@
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
+      <c r="M66" s="8" t="n"/>
+      <c r="N66" s="8" t="n"/>
+      <c r="O66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
@@ -1644,6 +1876,9 @@
       <c r="J67" s="8" t="n"/>
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="8" t="n"/>
+      <c r="M67" s="8" t="n"/>
+      <c r="N67" s="8" t="n"/>
+      <c r="O67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -1658,6 +1893,9 @@
       <c r="J68" s="8" t="n"/>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
+      <c r="M68" s="8" t="n"/>
+      <c r="N68" s="8" t="n"/>
+      <c r="O68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
@@ -1672,6 +1910,9 @@
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="8" t="n"/>
+      <c r="O69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -1686,6 +1927,9 @@
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
+      <c r="M70" s="8" t="n"/>
+      <c r="N70" s="8" t="n"/>
+      <c r="O70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
@@ -1700,6 +1944,9 @@
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
       <c r="L71" s="8" t="n"/>
+      <c r="M71" s="8" t="n"/>
+      <c r="N71" s="8" t="n"/>
+      <c r="O71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -1714,6 +1961,9 @@
       <c r="J72" s="8" t="n"/>
       <c r="K72" s="8" t="n"/>
       <c r="L72" s="8" t="n"/>
+      <c r="M72" s="8" t="n"/>
+      <c r="N72" s="8" t="n"/>
+      <c r="O72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
@@ -1728,6 +1978,9 @@
       <c r="J73" s="8" t="n"/>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="8" t="n"/>
+      <c r="M73" s="8" t="n"/>
+      <c r="N73" s="8" t="n"/>
+      <c r="O73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -1742,6 +1995,9 @@
       <c r="J74" s="8" t="n"/>
       <c r="K74" s="8" t="n"/>
       <c r="L74" s="8" t="n"/>
+      <c r="M74" s="8" t="n"/>
+      <c r="N74" s="8" t="n"/>
+      <c r="O74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
@@ -1756,6 +2012,9 @@
       <c r="J75" s="8" t="n"/>
       <c r="K75" s="8" t="n"/>
       <c r="L75" s="8" t="n"/>
+      <c r="M75" s="8" t="n"/>
+      <c r="N75" s="8" t="n"/>
+      <c r="O75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -1770,6 +2029,9 @@
       <c r="J76" s="8" t="n"/>
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
+      <c r="M76" s="8" t="n"/>
+      <c r="N76" s="8" t="n"/>
+      <c r="O76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
@@ -1784,6 +2046,9 @@
       <c r="J77" s="8" t="n"/>
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
+      <c r="N77" s="8" t="n"/>
+      <c r="O77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -1798,6 +2063,9 @@
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
+      <c r="M78" s="8" t="n"/>
+      <c r="N78" s="8" t="n"/>
+      <c r="O78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
@@ -1812,6 +2080,9 @@
       <c r="J79" s="8" t="n"/>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
+      <c r="M79" s="8" t="n"/>
+      <c r="N79" s="8" t="n"/>
+      <c r="O79" s="8" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -1826,6 +2097,9 @@
       <c r="J80" s="8" t="n"/>
       <c r="K80" s="8" t="n"/>
       <c r="L80" s="8" t="n"/>
+      <c r="M80" s="8" t="n"/>
+      <c r="N80" s="8" t="n"/>
+      <c r="O80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
@@ -1840,6 +2114,9 @@
       <c r="J81" s="8" t="n"/>
       <c r="K81" s="8" t="n"/>
       <c r="L81" s="8" t="n"/>
+      <c r="M81" s="8" t="n"/>
+      <c r="N81" s="8" t="n"/>
+      <c r="O81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -1854,6 +2131,9 @@
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
       <c r="L82" s="8" t="n"/>
+      <c r="M82" s="8" t="n"/>
+      <c r="N82" s="8" t="n"/>
+      <c r="O82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
@@ -1868,6 +2148,9 @@
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="8" t="n"/>
+      <c r="M83" s="8" t="n"/>
+      <c r="N83" s="8" t="n"/>
+      <c r="O83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -1882,6 +2165,9 @@
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="8" t="n"/>
+      <c r="M84" s="8" t="n"/>
+      <c r="N84" s="8" t="n"/>
+      <c r="O84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n"/>
@@ -1896,6 +2182,9 @@
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
+      <c r="M85" s="8" t="n"/>
+      <c r="N85" s="8" t="n"/>
+      <c r="O85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -1910,6 +2199,9 @@
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
       <c r="L86" s="8" t="n"/>
+      <c r="M86" s="8" t="n"/>
+      <c r="N86" s="8" t="n"/>
+      <c r="O86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
@@ -1924,6 +2216,9 @@
       <c r="J87" s="8" t="n"/>
       <c r="K87" s="8" t="n"/>
       <c r="L87" s="8" t="n"/>
+      <c r="M87" s="8" t="n"/>
+      <c r="N87" s="8" t="n"/>
+      <c r="O87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -1938,6 +2233,9 @@
       <c r="J88" s="8" t="n"/>
       <c r="K88" s="8" t="n"/>
       <c r="L88" s="8" t="n"/>
+      <c r="M88" s="8" t="n"/>
+      <c r="N88" s="8" t="n"/>
+      <c r="O88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -1952,6 +2250,9 @@
       <c r="J89" s="8" t="n"/>
       <c r="K89" s="8" t="n"/>
       <c r="L89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
+      <c r="N89" s="8" t="n"/>
+      <c r="O89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -1966,6 +2267,9 @@
       <c r="J90" s="8" t="n"/>
       <c r="K90" s="8" t="n"/>
       <c r="L90" s="8" t="n"/>
+      <c r="M90" s="8" t="n"/>
+      <c r="N90" s="8" t="n"/>
+      <c r="O90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -1980,6 +2284,9 @@
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
       <c r="L91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
+      <c r="N91" s="8" t="n"/>
+      <c r="O91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -1994,6 +2301,9 @@
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
+      <c r="M92" s="8" t="n"/>
+      <c r="N92" s="8" t="n"/>
+      <c r="O92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -2008,6 +2318,9 @@
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
       <c r="L93" s="8" t="n"/>
+      <c r="M93" s="8" t="n"/>
+      <c r="N93" s="8" t="n"/>
+      <c r="O93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -2022,6 +2335,9 @@
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
+      <c r="M94" s="8" t="n"/>
+      <c r="N94" s="8" t="n"/>
+      <c r="O94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -2036,6 +2352,9 @@
       <c r="J95" s="8" t="n"/>
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="8" t="n"/>
+      <c r="M95" s="8" t="n"/>
+      <c r="N95" s="8" t="n"/>
+      <c r="O95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -2050,6 +2369,9 @@
       <c r="J96" s="8" t="n"/>
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="8" t="n"/>
+      <c r="M96" s="8" t="n"/>
+      <c r="N96" s="8" t="n"/>
+      <c r="O96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -2064,6 +2386,9 @@
       <c r="J97" s="8" t="n"/>
       <c r="K97" s="8" t="n"/>
       <c r="L97" s="8" t="n"/>
+      <c r="M97" s="8" t="n"/>
+      <c r="N97" s="8" t="n"/>
+      <c r="O97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -2078,6 +2403,9 @@
       <c r="J98" s="8" t="n"/>
       <c r="K98" s="8" t="n"/>
       <c r="L98" s="8" t="n"/>
+      <c r="M98" s="8" t="n"/>
+      <c r="N98" s="8" t="n"/>
+      <c r="O98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -2092,6 +2420,9 @@
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="8" t="n"/>
+      <c r="M99" s="8" t="n"/>
+      <c r="N99" s="8" t="n"/>
+      <c r="O99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -2106,13 +2437,16 @@
       <c r="J100" s="8" t="n"/>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
+      <c r="M100" s="8" t="n"/>
+      <c r="N100" s="8" t="n"/>
+      <c r="O100" s="8" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="F3:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"self,outsourced"</formula1>
     </dataValidation>
-    <dataValidation sqref="L3:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"quote,in_progress,done,delivered"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2130,9 +2464,9 @@
   <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
@@ -2897,12 +3231,12 @@
   <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3885,13 +4219,13 @@
   <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">

--- a/WAYTHAI-FORYOU_Template.xlsx
+++ b/WAYTHAI-FORYOU_Template.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="expenses" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_transactions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="employees" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="material_purchases" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,16 +498,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="125" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>WAYTHAI-FORYOU — แบบฟอร์มกรอกข้อมูล (ฉบับย่อ 4 ชีต)</t>
+          <t>WAYTHAI-FORYOU — แบบฟอร์มกรอกข้อมูล</t>
         </is>
       </c>
     </row>
@@ -516,7 +517,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>กรอกแค่ 4 ชีตนี้พอ:</t>
+          <t>ชีตที่กรอก:</t>
         </is>
       </c>
     </row>
@@ -526,66 +527,52 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>① ออเดอร์  — งานแต่ละงาน: ชื่อลูกค้า+เบอร์, ราคารวม, แล้วแยกต้นทุน 'ค่าไม้/ค่าสี/ค่าแรง/ค่าส่ง', มัดจำ</t>
+          <t>① ออเดอร์  — งาน: ลูกค้า+เบอร์, ราคารวม, ต้นทุนแยก ค่าไม้/ค่าสี/ค่าแรง/ค่าส่ง, แหล่งผลิต (self/outsourced), มัดจำ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">          ★ ระบบจะรวมต้นทุน = ไม้+สี+แรง+ส่ง เอง → คำนวณกำไรของงาน และดึง 'ค่าสี' ไปโชว์บน Dashboard ให้</t>
+          <t>② รายจ่าย  — ค่าใช้จ่ายไม่ผูกออเดอร์: ค่าเช่า=rent, โฆษณา=ads, ขายออนไลน์=marketing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">          ★ แหล่งผลิต: self=ผลิตเอง | outsourced=สั่งซัพ (กรณีสั่งซัพ ใส่ยอดจ่ายซัพในช่อง 'ค่าไม้')</t>
+          <t>③ เงินสด   — เงินเข้า-ออกจริง (รับ=in, จ่าย=out)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">          ★ ออเดอร์เดียวมีทั้งผลิตเอง+สั่งซัพ → แยกเป็น 2 แถว (รหัสต่างกัน)</t>
+          <t>④ พนักงาน  — production=ช่างไม้/ช่างสี, marketing=ขายออนไลน์</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>② รายจ่าย  — ค่าใช้จ่ายที่ไม่ผูกกับออเดอร์: ค่าเช่า=rent, โฆษณา=ads, ขายออนไลน์=marketing (อย่าใส่ค่าไม้/สีซ้ำที่นี่ถ้าใส่ในออเดอร์แล้ว)</t>
+          <t>⑤ ซื้อสี/วัตถุดิบ (material_purchases) — ประวัติซื้อสีแบบละเอียด (ร้าน/แบรนด์/ชนิดสี/รหัสสี/ราคา/VAT) → หน้า 'วิเคราะห์ค่าสี'</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>③ เงินสด   — เงินเข้า-ออกจริงในบัญชี (รับมัดจำ/ชำระ=in, จ่ายซัพ/เงินเดือน=out)</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>④ พนักงาน  — ช่างไม้/ช่างสี=production, คนขายออนไลน์=marketing</t>
+          <t>กติกา: แถว1=ชื่อไทย แถว2=ชื่อฟิลด์(ห้ามแก้) เริ่มกรอกแถว3 · ช่อง*สีเหลือง=จำเป็น · เงิน=บาท · วันที่=ปปปป-ดด-วว</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>กติกา: แถว1=ชื่อไทย แถว2=ชื่อฟิลด์(ห้ามแก้) เริ่มกรอกแถว3 · ช่อง*สีเหลือง=จำเป็น · เงิน=บาท · วันที่=ปปปป-ดด-วว · ช่องมีลูกศร=เลือกจากรายการ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>นำเข้า: เว็บ → แท็บ 'นำเข้าข้อมูล' → อัปโหลดไฟล์นี้ (ยิงซ้ำไม่เบิ้ล)</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>นำเข้า: เว็บ → 'นำเข้าข้อมูล' → อัปโหลดไฟล์นี้ (รองรับข้อมูลพันแถว ระบบทยอยส่งให้)</t>
         </is>
       </c>
     </row>
@@ -605,20 +592,20 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2464,9 +2451,9 @@
   <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
@@ -3231,12 +3218,12 @@
   <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4220,12 +4207,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5198,4 +5185,1861 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="005A9D77"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>รหัสรายการ*</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>วันที่*</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>ร้านค้า</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>เลข Inv</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>แบรนด์</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>ชนิดสี</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>เบส</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>รหัสสี</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>จำนวน</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>หน่วย</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>ราคา (บาท)</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>ราคารวมภาษี (บาท)</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>ราคาก่อนภาษี (บาท)</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>ยอดภาษี (บาท)</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>หมวด</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>external_id</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>purchase_date</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>inv_no</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>item_type</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>color_code</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>total_incl_vat</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>total_excl_vat</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>vat</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="8" t="n"/>
+      <c r="O4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+      <c r="L25" s="8" t="n"/>
+      <c r="M25" s="8" t="n"/>
+      <c r="N25" s="8" t="n"/>
+      <c r="O25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="8" t="n"/>
+      <c r="O26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
+      <c r="M27" s="8" t="n"/>
+      <c r="N27" s="8" t="n"/>
+      <c r="O27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="8" t="n"/>
+      <c r="O29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="8" t="n"/>
+      <c r="O30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="8" t="n"/>
+      <c r="N31" s="8" t="n"/>
+      <c r="O31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+      <c r="L33" s="8" t="n"/>
+      <c r="M33" s="8" t="n"/>
+      <c r="N33" s="8" t="n"/>
+      <c r="O33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
+      <c r="O34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
+      <c r="L35" s="8" t="n"/>
+      <c r="M35" s="8" t="n"/>
+      <c r="N35" s="8" t="n"/>
+      <c r="O35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="8" t="n"/>
+      <c r="O36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="8" t="n"/>
+      <c r="O37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="8" t="n"/>
+      <c r="O38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="8" t="n"/>
+      <c r="O39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+      <c r="L41" s="8" t="n"/>
+      <c r="M41" s="8" t="n"/>
+      <c r="N41" s="8" t="n"/>
+      <c r="O41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+      <c r="L42" s="8" t="n"/>
+      <c r="M42" s="8" t="n"/>
+      <c r="N42" s="8" t="n"/>
+      <c r="O42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="8" t="n"/>
+      <c r="M44" s="8" t="n"/>
+      <c r="N44" s="8" t="n"/>
+      <c r="O44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="8" t="n"/>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
+      <c r="L45" s="8" t="n"/>
+      <c r="M45" s="8" t="n"/>
+      <c r="N45" s="8" t="n"/>
+      <c r="O45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+      <c r="L46" s="8" t="n"/>
+      <c r="M46" s="8" t="n"/>
+      <c r="N46" s="8" t="n"/>
+      <c r="O46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="8" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
+      <c r="L47" s="8" t="n"/>
+      <c r="M47" s="8" t="n"/>
+      <c r="N47" s="8" t="n"/>
+      <c r="O47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="8" t="n"/>
+      <c r="N50" s="8" t="n"/>
+      <c r="O50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
+      <c r="N51" s="8" t="n"/>
+      <c r="O51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
+      <c r="M52" s="8" t="n"/>
+      <c r="N52" s="8" t="n"/>
+      <c r="O52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
+      <c r="M53" s="8" t="n"/>
+      <c r="N53" s="8" t="n"/>
+      <c r="O53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="8" t="n"/>
+      <c r="N54" s="8" t="n"/>
+      <c r="O54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
+      <c r="M55" s="8" t="n"/>
+      <c r="N55" s="8" t="n"/>
+      <c r="O55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
+      <c r="M56" s="8" t="n"/>
+      <c r="N56" s="8" t="n"/>
+      <c r="O56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+      <c r="M57" s="8" t="n"/>
+      <c r="N57" s="8" t="n"/>
+      <c r="O57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n"/>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="8" t="n"/>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
+      <c r="L58" s="8" t="n"/>
+      <c r="M58" s="8" t="n"/>
+      <c r="N58" s="8" t="n"/>
+      <c r="O58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
+      <c r="L59" s="8" t="n"/>
+      <c r="M59" s="8" t="n"/>
+      <c r="N59" s="8" t="n"/>
+      <c r="O59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
+      <c r="L60" s="8" t="n"/>
+      <c r="M60" s="8" t="n"/>
+      <c r="N60" s="8" t="n"/>
+      <c r="O60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="8" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
+      <c r="L61" s="8" t="n"/>
+      <c r="M61" s="8" t="n"/>
+      <c r="N61" s="8" t="n"/>
+      <c r="O61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n"/>
+      <c r="M62" s="8" t="n"/>
+      <c r="N62" s="8" t="n"/>
+      <c r="O62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="8" t="n"/>
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+      <c r="L63" s="8" t="n"/>
+      <c r="M63" s="8" t="n"/>
+      <c r="N63" s="8" t="n"/>
+      <c r="O63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+      <c r="G64" s="8" t="n"/>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+      <c r="L64" s="8" t="n"/>
+      <c r="M64" s="8" t="n"/>
+      <c r="N64" s="8" t="n"/>
+      <c r="O64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n"/>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="8" t="n"/>
+      <c r="F65" s="8" t="n"/>
+      <c r="G65" s="8" t="n"/>
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="8" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="8" t="n"/>
+      <c r="L65" s="8" t="n"/>
+      <c r="M65" s="8" t="n"/>
+      <c r="N65" s="8" t="n"/>
+      <c r="O65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="8" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="8" t="n"/>
+      <c r="M66" s="8" t="n"/>
+      <c r="N66" s="8" t="n"/>
+      <c r="O66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n"/>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="8" t="n"/>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="8" t="n"/>
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+      <c r="L67" s="8" t="n"/>
+      <c r="M67" s="8" t="n"/>
+      <c r="N67" s="8" t="n"/>
+      <c r="O67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n"/>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="8" t="n"/>
+      <c r="G68" s="8" t="n"/>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+      <c r="L68" s="8" t="n"/>
+      <c r="M68" s="8" t="n"/>
+      <c r="N68" s="8" t="n"/>
+      <c r="O68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n"/>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="8" t="n"/>
+      <c r="O69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n"/>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
+      <c r="G70" s="8" t="n"/>
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
+      <c r="L70" s="8" t="n"/>
+      <c r="M70" s="8" t="n"/>
+      <c r="N70" s="8" t="n"/>
+      <c r="O70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="8" t="n"/>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="8" t="n"/>
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="8" t="n"/>
+      <c r="J71" s="8" t="n"/>
+      <c r="K71" s="8" t="n"/>
+      <c r="L71" s="8" t="n"/>
+      <c r="M71" s="8" t="n"/>
+      <c r="N71" s="8" t="n"/>
+      <c r="O71" s="8" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
+      <c r="G72" s="8" t="n"/>
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="8" t="n"/>
+      <c r="J72" s="8" t="n"/>
+      <c r="K72" s="8" t="n"/>
+      <c r="L72" s="8" t="n"/>
+      <c r="M72" s="8" t="n"/>
+      <c r="N72" s="8" t="n"/>
+      <c r="O72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="8" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="8" t="n"/>
+      <c r="J73" s="8" t="n"/>
+      <c r="K73" s="8" t="n"/>
+      <c r="L73" s="8" t="n"/>
+      <c r="M73" s="8" t="n"/>
+      <c r="N73" s="8" t="n"/>
+      <c r="O73" s="8" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n"/>
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="8" t="n"/>
+      <c r="G74" s="8" t="n"/>
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="8" t="n"/>
+      <c r="J74" s="8" t="n"/>
+      <c r="K74" s="8" t="n"/>
+      <c r="L74" s="8" t="n"/>
+      <c r="M74" s="8" t="n"/>
+      <c r="N74" s="8" t="n"/>
+      <c r="O74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="8" t="n"/>
+      <c r="J75" s="8" t="n"/>
+      <c r="K75" s="8" t="n"/>
+      <c r="L75" s="8" t="n"/>
+      <c r="M75" s="8" t="n"/>
+      <c r="N75" s="8" t="n"/>
+      <c r="O75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="8" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+      <c r="L76" s="8" t="n"/>
+      <c r="M76" s="8" t="n"/>
+      <c r="N76" s="8" t="n"/>
+      <c r="O76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
+      <c r="N77" s="8" t="n"/>
+      <c r="O77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n"/>
+      <c r="B78" s="7" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
+      <c r="G78" s="8" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
+      <c r="L78" s="8" t="n"/>
+      <c r="M78" s="8" t="n"/>
+      <c r="N78" s="8" t="n"/>
+      <c r="O78" s="8" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n"/>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="8" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="8" t="n"/>
+      <c r="F79" s="8" t="n"/>
+      <c r="G79" s="8" t="n"/>
+      <c r="H79" s="8" t="n"/>
+      <c r="I79" s="8" t="n"/>
+      <c r="J79" s="8" t="n"/>
+      <c r="K79" s="8" t="n"/>
+      <c r="L79" s="8" t="n"/>
+      <c r="M79" s="8" t="n"/>
+      <c r="N79" s="8" t="n"/>
+      <c r="O79" s="8" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n"/>
+      <c r="B80" s="7" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="8" t="n"/>
+      <c r="F80" s="8" t="n"/>
+      <c r="G80" s="8" t="n"/>
+      <c r="H80" s="8" t="n"/>
+      <c r="I80" s="8" t="n"/>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="8" t="n"/>
+      <c r="L80" s="8" t="n"/>
+      <c r="M80" s="8" t="n"/>
+      <c r="N80" s="8" t="n"/>
+      <c r="O80" s="8" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n"/>
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="8" t="n"/>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="8" t="n"/>
+      <c r="H81" s="8" t="n"/>
+      <c r="I81" s="8" t="n"/>
+      <c r="J81" s="8" t="n"/>
+      <c r="K81" s="8" t="n"/>
+      <c r="L81" s="8" t="n"/>
+      <c r="M81" s="8" t="n"/>
+      <c r="N81" s="8" t="n"/>
+      <c r="O81" s="8" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n"/>
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="8" t="n"/>
+      <c r="G82" s="8" t="n"/>
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="8" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
+      <c r="L82" s="8" t="n"/>
+      <c r="M82" s="8" t="n"/>
+      <c r="N82" s="8" t="n"/>
+      <c r="O82" s="8" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n"/>
+      <c r="B83" s="7" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="8" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
+      <c r="L83" s="8" t="n"/>
+      <c r="M83" s="8" t="n"/>
+      <c r="N83" s="8" t="n"/>
+      <c r="O83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n"/>
+      <c r="B84" s="7" t="n"/>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="8" t="n"/>
+      <c r="F84" s="8" t="n"/>
+      <c r="G84" s="8" t="n"/>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
+      <c r="L84" s="8" t="n"/>
+      <c r="M84" s="8" t="n"/>
+      <c r="N84" s="8" t="n"/>
+      <c r="O84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n"/>
+      <c r="B85" s="7" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="8" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
+      <c r="L85" s="8" t="n"/>
+      <c r="M85" s="8" t="n"/>
+      <c r="N85" s="8" t="n"/>
+      <c r="O85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n"/>
+      <c r="B86" s="7" t="n"/>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="8" t="n"/>
+      <c r="G86" s="8" t="n"/>
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="8" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
+      <c r="L86" s="8" t="n"/>
+      <c r="M86" s="8" t="n"/>
+      <c r="N86" s="8" t="n"/>
+      <c r="O86" s="8" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n"/>
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="8" t="n"/>
+      <c r="F87" s="8" t="n"/>
+      <c r="G87" s="8" t="n"/>
+      <c r="H87" s="8" t="n"/>
+      <c r="I87" s="8" t="n"/>
+      <c r="J87" s="8" t="n"/>
+      <c r="K87" s="8" t="n"/>
+      <c r="L87" s="8" t="n"/>
+      <c r="M87" s="8" t="n"/>
+      <c r="N87" s="8" t="n"/>
+      <c r="O87" s="8" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n"/>
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="8" t="n"/>
+      <c r="G88" s="8" t="n"/>
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="8" t="n"/>
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="8" t="n"/>
+      <c r="M88" s="8" t="n"/>
+      <c r="N88" s="8" t="n"/>
+      <c r="O88" s="8" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n"/>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
+      <c r="N89" s="8" t="n"/>
+      <c r="O89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n"/>
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="8" t="n"/>
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="8" t="n"/>
+      <c r="F90" s="8" t="n"/>
+      <c r="G90" s="8" t="n"/>
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="8" t="n"/>
+      <c r="J90" s="8" t="n"/>
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="8" t="n"/>
+      <c r="M90" s="8" t="n"/>
+      <c r="N90" s="8" t="n"/>
+      <c r="O90" s="8" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n"/>
+      <c r="B91" s="7" t="n"/>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="8" t="n"/>
+      <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
+      <c r="N91" s="8" t="n"/>
+      <c r="O91" s="8" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n"/>
+      <c r="B92" s="7" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="8" t="n"/>
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="8" t="n"/>
+      <c r="G92" s="8" t="n"/>
+      <c r="H92" s="8" t="n"/>
+      <c r="I92" s="8" t="n"/>
+      <c r="J92" s="8" t="n"/>
+      <c r="K92" s="8" t="n"/>
+      <c r="L92" s="8" t="n"/>
+      <c r="M92" s="8" t="n"/>
+      <c r="N92" s="8" t="n"/>
+      <c r="O92" s="8" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n"/>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="8" t="n"/>
+      <c r="J93" s="8" t="n"/>
+      <c r="K93" s="8" t="n"/>
+      <c r="L93" s="8" t="n"/>
+      <c r="M93" s="8" t="n"/>
+      <c r="N93" s="8" t="n"/>
+      <c r="O93" s="8" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n"/>
+      <c r="B94" s="7" t="n"/>
+      <c r="C94" s="8" t="n"/>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="8" t="n"/>
+      <c r="G94" s="8" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="8" t="n"/>
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
+      <c r="L94" s="8" t="n"/>
+      <c r="M94" s="8" t="n"/>
+      <c r="N94" s="8" t="n"/>
+      <c r="O94" s="8" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n"/>
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="8" t="n"/>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="8" t="n"/>
+      <c r="H95" s="8" t="n"/>
+      <c r="I95" s="8" t="n"/>
+      <c r="J95" s="8" t="n"/>
+      <c r="K95" s="8" t="n"/>
+      <c r="L95" s="8" t="n"/>
+      <c r="M95" s="8" t="n"/>
+      <c r="N95" s="8" t="n"/>
+      <c r="O95" s="8" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n"/>
+      <c r="B96" s="7" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="8" t="n"/>
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="8" t="n"/>
+      <c r="M96" s="8" t="n"/>
+      <c r="N96" s="8" t="n"/>
+      <c r="O96" s="8" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n"/>
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="8" t="n"/>
+      <c r="J97" s="8" t="n"/>
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="8" t="n"/>
+      <c r="M97" s="8" t="n"/>
+      <c r="N97" s="8" t="n"/>
+      <c r="O97" s="8" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n"/>
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="8" t="n"/>
+      <c r="F98" s="8" t="n"/>
+      <c r="G98" s="8" t="n"/>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="8" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
+      <c r="L98" s="8" t="n"/>
+      <c r="M98" s="8" t="n"/>
+      <c r="N98" s="8" t="n"/>
+      <c r="O98" s="8" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n"/>
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="8" t="n"/>
+      <c r="F99" s="8" t="n"/>
+      <c r="G99" s="8" t="n"/>
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="8" t="n"/>
+      <c r="J99" s="8" t="n"/>
+      <c r="K99" s="8" t="n"/>
+      <c r="L99" s="8" t="n"/>
+      <c r="M99" s="8" t="n"/>
+      <c r="N99" s="8" t="n"/>
+      <c r="O99" s="8" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n"/>
+      <c r="B100" s="7" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="8" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="8" t="n"/>
+      <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
+      <c r="L100" s="8" t="n"/>
+      <c r="M100" s="8" t="n"/>
+      <c r="N100" s="8" t="n"/>
+      <c r="O100" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="O3:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"paint,wood,hardware,other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/WAYTHAI-FORYOU_Template.xlsx
+++ b/WAYTHAI-FORYOU_Template.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +69,18 @@
       <color rgb="001F3A5F"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E5A34"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B00020"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +112,11 @@
         <fgColor rgb="00DCE9F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE7E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -129,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -151,6 +166,15 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -225,6 +249,91 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>WAYTHAI-FORYOU</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>เติมข้อมูลใหม่ 'ต่อท้ายแถวล่างสุด' เท่านั้น
+ห้ามแทรกกลาง / เรียงใหม่ / ลบแถวเก่า
+(ดูรายละเอียดที่ชีต 'วิธีใช้')</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>WAYTHAI-FORYOU</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>เติมข้อมูลใหม่ 'ต่อท้ายแถวล่างสุด' เท่านั้น
+ห้ามแทรกกลาง / เรียงใหม่ / ลบแถวเก่า
+(ดูรายละเอียดที่ชีต 'วิธีใช้')</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>WAYTHAI-FORYOU</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>เติมข้อมูลใหม่ 'ต่อท้ายแถวล่างสุด' เท่านั้น
+ห้ามแทรกกลาง / เรียงใหม่ / ลบแถวเก่า
+(ดูรายละเอียดที่ชีต 'วิธีใช้')</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>WAYTHAI-FORYOU</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>เติมข้อมูลใหม่ 'ต่อท้ายแถวล่างสุด' เท่านั้น
+ห้ามแทรกกลาง / เรียงใหม่ / ลบแถวเก่า
+(ดูรายละเอียดที่ชีต 'วิธีใช้')</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>WAYTHAI-FORYOU</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>เติมข้อมูลใหม่ 'ต่อท้ายแถวล่างสุด' เท่านั้น
+ห้ามแทรกกลาง / เรียงใหม่ / ลบแถวเก่า
+(ดูรายละเอียดที่ชีต 'วิธีใช้')</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -517,10 +626,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="135" customWidth="1" min="1" max="1"/>
+    <col width="98" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,6 +700,102 @@
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>นำเข้า: เว็บ → 'นำเข้าข้อมูล' → อัปโหลดไฟล์นี้ (อัปซ้ำไฟล์เดิมได้ ไม่เบิ้ล)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>══════════════════════════════════════════════════</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ การอัปเดตข้อมูลเดือนใหม่ — อ่านให้ครบ (กันข้อมูลเบิ้ล)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>══════════════════════════════════════════════════</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>วิธีที่ถูก:  เปิดไฟล์เดิมไฟล์นี้ → พิมพ์ข้อมูลเดือนใหม่ 'ต่อท้ายแถวล่างสุด' เท่านั้น → บันทึกชื่อไฟล์เดิม → อัปโหลดซ้ำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            ระบบจะรู้ว่าแถวเก่าคือของเดิม (ไม่เพิ่มซ้ำ) และเพิ่มเฉพาะแถวใหม่ให้เอง</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>ห้ามเด็ดขาด (จะทำให้ข้อมูลเบิ้ล / ผิดเพี้ยน):</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ✗ ห้ามแทรกแถวกลางๆ ระหว่างของเดิม</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ✗ ห้ามเรียง/sort ข้อมูลใหม่</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ✗ ห้ามลบแถวเก่าทิ้ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ✗ ห้ามสลับลำดับคอลัมน์ หรือแก้ชื่อฟิลด์ (แถวที่ 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>เพิ่มได้อย่างเดียว = พิมพ์ต่อจากแถวสุดท้ายลงไปข้างล่าง</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>ถ้าเผลอทำผิด/ข้อมูลมั่ว: ไม่ต้องกังวล — แก้ไฟล์ให้ถูกแล้วอัปโหลดชื่อไฟล์เดิมใหม่ทั้งไฟล์ ระบบจะทับให้เป็นชุดล่าสุด</t>
         </is>
       </c>
     </row>
@@ -2864,6 +3069,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3935,6 +4141,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -5230,6 +5437,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -6221,6 +6429,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -8382,5 +8591,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/WAYTHAI-FORYOU_Template.xlsx
+++ b/WAYTHAI-FORYOU_Template.xlsx
@@ -12,7 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="expenses" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_transactions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="employees" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="material_purchases" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,6 +280,13 @@
 (ดูรายละเอียดที่ชีต 'วิธีใช้')</t>
       </text>
     </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>ค่าสีและวัสดุทุกชนิด บันทึกที่ชีตนี้
+เลือก category = paint / wood / hardware / labor
+(ไม่มีชีต material แยกแล้ว)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -303,23 +309,6 @@
 </file>
 
 <file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>WAYTHAI-FORYOU</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>เติมข้อมูลใหม่ 'ต่อท้ายแถวล่างสุด' เท่านั้น
-ห้ามแทรกกลาง / เรียงใหม่ / ลบแถวเก่า
-(ดูรายละเอียดที่ชีต 'วิธีใช้')</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>WAYTHAI-FORYOU</author>
@@ -626,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="98" customWidth="1" min="1" max="1"/>
@@ -655,7 +644,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>① ออเดอร์ ② รายจ่าย ③ เงินสด ④ พนักงาน ⑤ ซื้อสี/วัตถุดิบ</t>
+          <t>① ออเดอร์ ② รายจ่าย(รวมค่าสี/วัสดุ) ③ เงินสด ④ พนักงาน</t>
         </is>
       </c>
     </row>
@@ -703,6 +692,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr"/>
     </row>
@@ -796,6 +786,13 @@
       <c r="A30" s="13" t="inlineStr">
         <is>
           <t>ถ้าเผลอทำผิด/ข้อมูลมั่ว: ไม่ต้องกังวล — แก้ไฟล์ให้ถูกแล้วอัปโหลดชื่อไฟล์เดิมใหม่ทั้งไฟล์ ระบบจะทับให้เป็นชุดล่าสุด</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>★ ค่าสี/วัสดุ: บันทึกในชีต 'รายจ่าย (expenses)' เลือก category = paint/wood/hardware/labor (ยกเลิกชีต material_purchases แล้ว — ที่เดียวจบ)</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3100,7 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>หมวด*</t>
+          <t>หมวด* (ค่าสี=paint, ไม้=wood, ฮาร์ดแวร์=hardware, ค่าแรง=labor / ดำเนินงาน=rent,utility,marketing,ads,transport,other)</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -3113,7 +3110,7 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>รายการ/หมายเหตุ</t>
+          <t>รายการ/หมายเหตุ (เช่น ร้านที่ซื้อ/แบรนด์สี)</t>
         </is>
       </c>
     </row>
@@ -6431,2166 +6428,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="005A9D77"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O200"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>รหัสรายการ*</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>วันที่* (วว/ดด/ปปปป)</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>ร้านค้า</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>เลข Inv</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>แบรนด์</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>ชนิดสี</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>เบส</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>รหัสสี</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>จำนวน</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>หน่วย</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>ราคา (บาท)</t>
-        </is>
-      </c>
-      <c r="L1" s="5" t="inlineStr">
-        <is>
-          <t>ราคารวมภาษี (บาท)</t>
-        </is>
-      </c>
-      <c r="M1" s="5" t="inlineStr">
-        <is>
-          <t>ราคาก่อนภาษี (บาท)</t>
-        </is>
-      </c>
-      <c r="N1" s="5" t="inlineStr">
-        <is>
-          <t>ยอดภาษี (บาท)</t>
-        </is>
-      </c>
-      <c r="O1" s="5" t="inlineStr">
-        <is>
-          <t>หมวด</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>external_id</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>purchase_date</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>vendor</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>inv_no</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>item_type</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>color_code</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>qty</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>unit_price</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>total_incl_vat</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="inlineStr">
-        <is>
-          <t>total_excl_vat</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>vat</t>
-        </is>
-      </c>
-      <c r="O2" s="7" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="M3" s="9" t="n"/>
-      <c r="N3" s="9" t="n"/>
-      <c r="O3" s="9" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="9" t="n"/>
-      <c r="O4" s="9" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="9" t="n"/>
-      <c r="O5" s="9" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="9" t="n"/>
-      <c r="O6" s="9" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="9" t="n"/>
-      <c r="O7" s="9" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="9" t="n"/>
-      <c r="O8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="9" t="n"/>
-      <c r="O9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="9" t="n"/>
-      <c r="O10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="9" t="n"/>
-      <c r="O11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="9" t="n"/>
-      <c r="O12" s="9" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="9" t="n"/>
-      <c r="O13" s="9" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="9" t="n"/>
-      <c r="O14" s="9" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n"/>
-      <c r="N15" s="9" t="n"/>
-      <c r="O15" s="9" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
-      <c r="O16" s="9" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="9" t="n"/>
-      <c r="O18" s="9" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
-      <c r="O19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="9" t="n"/>
-      <c r="N20" s="9" t="n"/>
-      <c r="O20" s="9" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
-      <c r="O21" s="9" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="9" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n"/>
-      <c r="O23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="9" t="n"/>
-      <c r="M24" s="9" t="n"/>
-      <c r="N24" s="9" t="n"/>
-      <c r="O24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
-      <c r="O25" s="9" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="9" t="n"/>
-      <c r="N26" s="9" t="n"/>
-      <c r="O26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="9" t="n"/>
-      <c r="N27" s="9" t="n"/>
-      <c r="O27" s="9" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="9" t="n"/>
-      <c r="O28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="9" t="n"/>
-      <c r="M29" s="9" t="n"/>
-      <c r="N29" s="9" t="n"/>
-      <c r="O29" s="9" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
-      <c r="L30" s="9" t="n"/>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="9" t="n"/>
-      <c r="O30" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
-      <c r="L31" s="9" t="n"/>
-      <c r="M31" s="9" t="n"/>
-      <c r="N31" s="9" t="n"/>
-      <c r="O31" s="9" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
-      <c r="L32" s="9" t="n"/>
-      <c r="M32" s="9" t="n"/>
-      <c r="N32" s="9" t="n"/>
-      <c r="O32" s="9" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
-      <c r="L33" s="9" t="n"/>
-      <c r="M33" s="9" t="n"/>
-      <c r="N33" s="9" t="n"/>
-      <c r="O33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="9" t="n"/>
-      <c r="L34" s="9" t="n"/>
-      <c r="M34" s="9" t="n"/>
-      <c r="N34" s="9" t="n"/>
-      <c r="O34" s="9" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="9" t="n"/>
-      <c r="M35" s="9" t="n"/>
-      <c r="N35" s="9" t="n"/>
-      <c r="O35" s="9" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="9" t="n"/>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="9" t="n"/>
-      <c r="O36" s="9" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
-      <c r="L37" s="9" t="n"/>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="9" t="n"/>
-      <c r="O37" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
-      <c r="L38" s="9" t="n"/>
-      <c r="M38" s="9" t="n"/>
-      <c r="N38" s="9" t="n"/>
-      <c r="O38" s="9" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="9" t="n"/>
-      <c r="N39" s="9" t="n"/>
-      <c r="O39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="9" t="n"/>
-      <c r="N40" s="9" t="n"/>
-      <c r="O40" s="9" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="n"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="9" t="n"/>
-      <c r="N41" s="9" t="n"/>
-      <c r="O41" s="9" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="n"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
-      <c r="L42" s="9" t="n"/>
-      <c r="M42" s="9" t="n"/>
-      <c r="N42" s="9" t="n"/>
-      <c r="O42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
-      <c r="L43" s="9" t="n"/>
-      <c r="M43" s="9" t="n"/>
-      <c r="N43" s="9" t="n"/>
-      <c r="O43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
-      <c r="L44" s="9" t="n"/>
-      <c r="M44" s="9" t="n"/>
-      <c r="N44" s="9" t="n"/>
-      <c r="O44" s="9" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="9" t="n"/>
-      <c r="L45" s="9" t="n"/>
-      <c r="M45" s="9" t="n"/>
-      <c r="N45" s="9" t="n"/>
-      <c r="O45" s="9" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="9" t="n"/>
-      <c r="L46" s="9" t="n"/>
-      <c r="M46" s="9" t="n"/>
-      <c r="N46" s="9" t="n"/>
-      <c r="O46" s="9" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="n"/>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="9" t="n"/>
-      <c r="L47" s="9" t="n"/>
-      <c r="M47" s="9" t="n"/>
-      <c r="N47" s="9" t="n"/>
-      <c r="O47" s="9" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="n"/>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n"/>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="9" t="n"/>
-      <c r="I48" s="9" t="n"/>
-      <c r="J48" s="9" t="n"/>
-      <c r="K48" s="9" t="n"/>
-      <c r="L48" s="9" t="n"/>
-      <c r="M48" s="9" t="n"/>
-      <c r="N48" s="9" t="n"/>
-      <c r="O48" s="9" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="n"/>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="9" t="n"/>
-      <c r="E49" s="9" t="n"/>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="9" t="n"/>
-      <c r="H49" s="9" t="n"/>
-      <c r="I49" s="9" t="n"/>
-      <c r="J49" s="9" t="n"/>
-      <c r="K49" s="9" t="n"/>
-      <c r="L49" s="9" t="n"/>
-      <c r="M49" s="9" t="n"/>
-      <c r="N49" s="9" t="n"/>
-      <c r="O49" s="9" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="n"/>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="9" t="n"/>
-      <c r="D50" s="9" t="n"/>
-      <c r="E50" s="9" t="n"/>
-      <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="9" t="n"/>
-      <c r="I50" s="9" t="n"/>
-      <c r="J50" s="9" t="n"/>
-      <c r="K50" s="9" t="n"/>
-      <c r="L50" s="9" t="n"/>
-      <c r="M50" s="9" t="n"/>
-      <c r="N50" s="9" t="n"/>
-      <c r="O50" s="9" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="n"/>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="9" t="n"/>
-      <c r="K51" s="9" t="n"/>
-      <c r="L51" s="9" t="n"/>
-      <c r="M51" s="9" t="n"/>
-      <c r="N51" s="9" t="n"/>
-      <c r="O51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="n"/>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="9" t="n"/>
-      <c r="I52" s="9" t="n"/>
-      <c r="J52" s="9" t="n"/>
-      <c r="K52" s="9" t="n"/>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="9" t="n"/>
-      <c r="N52" s="9" t="n"/>
-      <c r="O52" s="9" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="n"/>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="9" t="n"/>
-      <c r="D53" s="9" t="n"/>
-      <c r="E53" s="9" t="n"/>
-      <c r="F53" s="9" t="n"/>
-      <c r="G53" s="9" t="n"/>
-      <c r="H53" s="9" t="n"/>
-      <c r="I53" s="9" t="n"/>
-      <c r="J53" s="9" t="n"/>
-      <c r="K53" s="9" t="n"/>
-      <c r="L53" s="9" t="n"/>
-      <c r="M53" s="9" t="n"/>
-      <c r="N53" s="9" t="n"/>
-      <c r="O53" s="9" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="n"/>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="9" t="n"/>
-      <c r="E54" s="9" t="n"/>
-      <c r="F54" s="9" t="n"/>
-      <c r="G54" s="9" t="n"/>
-      <c r="H54" s="9" t="n"/>
-      <c r="I54" s="9" t="n"/>
-      <c r="J54" s="9" t="n"/>
-      <c r="K54" s="9" t="n"/>
-      <c r="L54" s="9" t="n"/>
-      <c r="M54" s="9" t="n"/>
-      <c r="N54" s="9" t="n"/>
-      <c r="O54" s="9" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="n"/>
-      <c r="B55" s="10" t="n"/>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
-      <c r="F55" s="9" t="n"/>
-      <c r="G55" s="9" t="n"/>
-      <c r="H55" s="9" t="n"/>
-      <c r="I55" s="9" t="n"/>
-      <c r="J55" s="9" t="n"/>
-      <c r="K55" s="9" t="n"/>
-      <c r="L55" s="9" t="n"/>
-      <c r="M55" s="9" t="n"/>
-      <c r="N55" s="9" t="n"/>
-      <c r="O55" s="9" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="n"/>
-      <c r="B56" s="10" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
-      <c r="L56" s="9" t="n"/>
-      <c r="M56" s="9" t="n"/>
-      <c r="N56" s="9" t="n"/>
-      <c r="O56" s="9" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="9" t="n"/>
-      <c r="D57" s="9" t="n"/>
-      <c r="E57" s="9" t="n"/>
-      <c r="F57" s="9" t="n"/>
-      <c r="G57" s="9" t="n"/>
-      <c r="H57" s="9" t="n"/>
-      <c r="I57" s="9" t="n"/>
-      <c r="J57" s="9" t="n"/>
-      <c r="K57" s="9" t="n"/>
-      <c r="L57" s="9" t="n"/>
-      <c r="M57" s="9" t="n"/>
-      <c r="N57" s="9" t="n"/>
-      <c r="O57" s="9" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="9" t="n"/>
-      <c r="D58" s="9" t="n"/>
-      <c r="E58" s="9" t="n"/>
-      <c r="F58" s="9" t="n"/>
-      <c r="G58" s="9" t="n"/>
-      <c r="H58" s="9" t="n"/>
-      <c r="I58" s="9" t="n"/>
-      <c r="J58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
-      <c r="L58" s="9" t="n"/>
-      <c r="M58" s="9" t="n"/>
-      <c r="N58" s="9" t="n"/>
-      <c r="O58" s="9" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="n"/>
-      <c r="B59" s="10" t="n"/>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="9" t="n"/>
-      <c r="G59" s="9" t="n"/>
-      <c r="H59" s="9" t="n"/>
-      <c r="I59" s="9" t="n"/>
-      <c r="J59" s="9" t="n"/>
-      <c r="K59" s="9" t="n"/>
-      <c r="L59" s="9" t="n"/>
-      <c r="M59" s="9" t="n"/>
-      <c r="N59" s="9" t="n"/>
-      <c r="O59" s="9" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="n"/>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="9" t="n"/>
-      <c r="D60" s="9" t="n"/>
-      <c r="E60" s="9" t="n"/>
-      <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
-      <c r="H60" s="9" t="n"/>
-      <c r="I60" s="9" t="n"/>
-      <c r="J60" s="9" t="n"/>
-      <c r="K60" s="9" t="n"/>
-      <c r="L60" s="9" t="n"/>
-      <c r="M60" s="9" t="n"/>
-      <c r="N60" s="9" t="n"/>
-      <c r="O60" s="9" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="n"/>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="9" t="n"/>
-      <c r="D61" s="9" t="n"/>
-      <c r="E61" s="9" t="n"/>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
-      <c r="H61" s="9" t="n"/>
-      <c r="I61" s="9" t="n"/>
-      <c r="J61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
-      <c r="L61" s="9" t="n"/>
-      <c r="M61" s="9" t="n"/>
-      <c r="N61" s="9" t="n"/>
-      <c r="O61" s="9" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="n"/>
-      <c r="B62" s="10" t="n"/>
-      <c r="C62" s="9" t="n"/>
-      <c r="D62" s="9" t="n"/>
-      <c r="E62" s="9" t="n"/>
-      <c r="F62" s="9" t="n"/>
-      <c r="G62" s="9" t="n"/>
-      <c r="H62" s="9" t="n"/>
-      <c r="I62" s="9" t="n"/>
-      <c r="J62" s="9" t="n"/>
-      <c r="K62" s="9" t="n"/>
-      <c r="L62" s="9" t="n"/>
-      <c r="M62" s="9" t="n"/>
-      <c r="N62" s="9" t="n"/>
-      <c r="O62" s="9" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="n"/>
-      <c r="B63" s="10" t="n"/>
-      <c r="C63" s="9" t="n"/>
-      <c r="D63" s="9" t="n"/>
-      <c r="E63" s="9" t="n"/>
-      <c r="F63" s="9" t="n"/>
-      <c r="G63" s="9" t="n"/>
-      <c r="H63" s="9" t="n"/>
-      <c r="I63" s="9" t="n"/>
-      <c r="J63" s="9" t="n"/>
-      <c r="K63" s="9" t="n"/>
-      <c r="L63" s="9" t="n"/>
-      <c r="M63" s="9" t="n"/>
-      <c r="N63" s="9" t="n"/>
-      <c r="O63" s="9" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="8" t="n"/>
-      <c r="B64" s="10" t="n"/>
-      <c r="C64" s="9" t="n"/>
-      <c r="D64" s="9" t="n"/>
-      <c r="E64" s="9" t="n"/>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="9" t="n"/>
-      <c r="H64" s="9" t="n"/>
-      <c r="I64" s="9" t="n"/>
-      <c r="J64" s="9" t="n"/>
-      <c r="K64" s="9" t="n"/>
-      <c r="L64" s="9" t="n"/>
-      <c r="M64" s="9" t="n"/>
-      <c r="N64" s="9" t="n"/>
-      <c r="O64" s="9" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="n"/>
-      <c r="B65" s="10" t="n"/>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="9" t="n"/>
-      <c r="E65" s="9" t="n"/>
-      <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
-      <c r="H65" s="9" t="n"/>
-      <c r="I65" s="9" t="n"/>
-      <c r="J65" s="9" t="n"/>
-      <c r="K65" s="9" t="n"/>
-      <c r="L65" s="9" t="n"/>
-      <c r="M65" s="9" t="n"/>
-      <c r="N65" s="9" t="n"/>
-      <c r="O65" s="9" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="8" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="9" t="n"/>
-      <c r="D66" s="9" t="n"/>
-      <c r="E66" s="9" t="n"/>
-      <c r="F66" s="9" t="n"/>
-      <c r="G66" s="9" t="n"/>
-      <c r="H66" s="9" t="n"/>
-      <c r="I66" s="9" t="n"/>
-      <c r="J66" s="9" t="n"/>
-      <c r="K66" s="9" t="n"/>
-      <c r="L66" s="9" t="n"/>
-      <c r="M66" s="9" t="n"/>
-      <c r="N66" s="9" t="n"/>
-      <c r="O66" s="9" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="9" t="n"/>
-      <c r="E67" s="9" t="n"/>
-      <c r="F67" s="9" t="n"/>
-      <c r="G67" s="9" t="n"/>
-      <c r="H67" s="9" t="n"/>
-      <c r="I67" s="9" t="n"/>
-      <c r="J67" s="9" t="n"/>
-      <c r="K67" s="9" t="n"/>
-      <c r="L67" s="9" t="n"/>
-      <c r="M67" s="9" t="n"/>
-      <c r="N67" s="9" t="n"/>
-      <c r="O67" s="9" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="n"/>
-      <c r="B68" s="10" t="n"/>
-      <c r="C68" s="9" t="n"/>
-      <c r="D68" s="9" t="n"/>
-      <c r="E68" s="9" t="n"/>
-      <c r="F68" s="9" t="n"/>
-      <c r="G68" s="9" t="n"/>
-      <c r="H68" s="9" t="n"/>
-      <c r="I68" s="9" t="n"/>
-      <c r="J68" s="9" t="n"/>
-      <c r="K68" s="9" t="n"/>
-      <c r="L68" s="9" t="n"/>
-      <c r="M68" s="9" t="n"/>
-      <c r="N68" s="9" t="n"/>
-      <c r="O68" s="9" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="n"/>
-      <c r="B69" s="10" t="n"/>
-      <c r="C69" s="9" t="n"/>
-      <c r="D69" s="9" t="n"/>
-      <c r="E69" s="9" t="n"/>
-      <c r="F69" s="9" t="n"/>
-      <c r="G69" s="9" t="n"/>
-      <c r="H69" s="9" t="n"/>
-      <c r="I69" s="9" t="n"/>
-      <c r="J69" s="9" t="n"/>
-      <c r="K69" s="9" t="n"/>
-      <c r="L69" s="9" t="n"/>
-      <c r="M69" s="9" t="n"/>
-      <c r="N69" s="9" t="n"/>
-      <c r="O69" s="9" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="n"/>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="9" t="n"/>
-      <c r="D70" s="9" t="n"/>
-      <c r="E70" s="9" t="n"/>
-      <c r="F70" s="9" t="n"/>
-      <c r="G70" s="9" t="n"/>
-      <c r="H70" s="9" t="n"/>
-      <c r="I70" s="9" t="n"/>
-      <c r="J70" s="9" t="n"/>
-      <c r="K70" s="9" t="n"/>
-      <c r="L70" s="9" t="n"/>
-      <c r="M70" s="9" t="n"/>
-      <c r="N70" s="9" t="n"/>
-      <c r="O70" s="9" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="n"/>
-      <c r="B71" s="10" t="n"/>
-      <c r="C71" s="9" t="n"/>
-      <c r="D71" s="9" t="n"/>
-      <c r="E71" s="9" t="n"/>
-      <c r="F71" s="9" t="n"/>
-      <c r="G71" s="9" t="n"/>
-      <c r="H71" s="9" t="n"/>
-      <c r="I71" s="9" t="n"/>
-      <c r="J71" s="9" t="n"/>
-      <c r="K71" s="9" t="n"/>
-      <c r="L71" s="9" t="n"/>
-      <c r="M71" s="9" t="n"/>
-      <c r="N71" s="9" t="n"/>
-      <c r="O71" s="9" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="n"/>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="9" t="n"/>
-      <c r="D72" s="9" t="n"/>
-      <c r="E72" s="9" t="n"/>
-      <c r="F72" s="9" t="n"/>
-      <c r="G72" s="9" t="n"/>
-      <c r="H72" s="9" t="n"/>
-      <c r="I72" s="9" t="n"/>
-      <c r="J72" s="9" t="n"/>
-      <c r="K72" s="9" t="n"/>
-      <c r="L72" s="9" t="n"/>
-      <c r="M72" s="9" t="n"/>
-      <c r="N72" s="9" t="n"/>
-      <c r="O72" s="9" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="n"/>
-      <c r="B73" s="10" t="n"/>
-      <c r="C73" s="9" t="n"/>
-      <c r="D73" s="9" t="n"/>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
-      <c r="H73" s="9" t="n"/>
-      <c r="I73" s="9" t="n"/>
-      <c r="J73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
-      <c r="L73" s="9" t="n"/>
-      <c r="M73" s="9" t="n"/>
-      <c r="N73" s="9" t="n"/>
-      <c r="O73" s="9" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="n"/>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="9" t="n"/>
-      <c r="H74" s="9" t="n"/>
-      <c r="I74" s="9" t="n"/>
-      <c r="J74" s="9" t="n"/>
-      <c r="K74" s="9" t="n"/>
-      <c r="L74" s="9" t="n"/>
-      <c r="M74" s="9" t="n"/>
-      <c r="N74" s="9" t="n"/>
-      <c r="O74" s="9" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="n"/>
-      <c r="B75" s="10" t="n"/>
-      <c r="C75" s="9" t="n"/>
-      <c r="D75" s="9" t="n"/>
-      <c r="E75" s="9" t="n"/>
-      <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
-      <c r="H75" s="9" t="n"/>
-      <c r="I75" s="9" t="n"/>
-      <c r="J75" s="9" t="n"/>
-      <c r="K75" s="9" t="n"/>
-      <c r="L75" s="9" t="n"/>
-      <c r="M75" s="9" t="n"/>
-      <c r="N75" s="9" t="n"/>
-      <c r="O75" s="9" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="n"/>
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="9" t="n"/>
-      <c r="D76" s="9" t="n"/>
-      <c r="E76" s="9" t="n"/>
-      <c r="F76" s="9" t="n"/>
-      <c r="G76" s="9" t="n"/>
-      <c r="H76" s="9" t="n"/>
-      <c r="I76" s="9" t="n"/>
-      <c r="J76" s="9" t="n"/>
-      <c r="K76" s="9" t="n"/>
-      <c r="L76" s="9" t="n"/>
-      <c r="M76" s="9" t="n"/>
-      <c r="N76" s="9" t="n"/>
-      <c r="O76" s="9" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="8" t="n"/>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="9" t="n"/>
-      <c r="D77" s="9" t="n"/>
-      <c r="E77" s="9" t="n"/>
-      <c r="F77" s="9" t="n"/>
-      <c r="G77" s="9" t="n"/>
-      <c r="H77" s="9" t="n"/>
-      <c r="I77" s="9" t="n"/>
-      <c r="J77" s="9" t="n"/>
-      <c r="K77" s="9" t="n"/>
-      <c r="L77" s="9" t="n"/>
-      <c r="M77" s="9" t="n"/>
-      <c r="N77" s="9" t="n"/>
-      <c r="O77" s="9" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="8" t="n"/>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="9" t="n"/>
-      <c r="D78" s="9" t="n"/>
-      <c r="E78" s="9" t="n"/>
-      <c r="F78" s="9" t="n"/>
-      <c r="G78" s="9" t="n"/>
-      <c r="H78" s="9" t="n"/>
-      <c r="I78" s="9" t="n"/>
-      <c r="J78" s="9" t="n"/>
-      <c r="K78" s="9" t="n"/>
-      <c r="L78" s="9" t="n"/>
-      <c r="M78" s="9" t="n"/>
-      <c r="N78" s="9" t="n"/>
-      <c r="O78" s="9" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="8" t="n"/>
-      <c r="B79" s="10" t="n"/>
-      <c r="C79" s="9" t="n"/>
-      <c r="D79" s="9" t="n"/>
-      <c r="E79" s="9" t="n"/>
-      <c r="F79" s="9" t="n"/>
-      <c r="G79" s="9" t="n"/>
-      <c r="H79" s="9" t="n"/>
-      <c r="I79" s="9" t="n"/>
-      <c r="J79" s="9" t="n"/>
-      <c r="K79" s="9" t="n"/>
-      <c r="L79" s="9" t="n"/>
-      <c r="M79" s="9" t="n"/>
-      <c r="N79" s="9" t="n"/>
-      <c r="O79" s="9" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="n"/>
-      <c r="B80" s="10" t="n"/>
-      <c r="C80" s="9" t="n"/>
-      <c r="D80" s="9" t="n"/>
-      <c r="E80" s="9" t="n"/>
-      <c r="F80" s="9" t="n"/>
-      <c r="G80" s="9" t="n"/>
-      <c r="H80" s="9" t="n"/>
-      <c r="I80" s="9" t="n"/>
-      <c r="J80" s="9" t="n"/>
-      <c r="K80" s="9" t="n"/>
-      <c r="L80" s="9" t="n"/>
-      <c r="M80" s="9" t="n"/>
-      <c r="N80" s="9" t="n"/>
-      <c r="O80" s="9" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="n"/>
-      <c r="B81" s="10" t="n"/>
-      <c r="C81" s="9" t="n"/>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="9" t="n"/>
-      <c r="F81" s="9" t="n"/>
-      <c r="G81" s="9" t="n"/>
-      <c r="H81" s="9" t="n"/>
-      <c r="I81" s="9" t="n"/>
-      <c r="J81" s="9" t="n"/>
-      <c r="K81" s="9" t="n"/>
-      <c r="L81" s="9" t="n"/>
-      <c r="M81" s="9" t="n"/>
-      <c r="N81" s="9" t="n"/>
-      <c r="O81" s="9" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="n"/>
-      <c r="B82" s="10" t="n"/>
-      <c r="C82" s="9" t="n"/>
-      <c r="D82" s="9" t="n"/>
-      <c r="E82" s="9" t="n"/>
-      <c r="F82" s="9" t="n"/>
-      <c r="G82" s="9" t="n"/>
-      <c r="H82" s="9" t="n"/>
-      <c r="I82" s="9" t="n"/>
-      <c r="J82" s="9" t="n"/>
-      <c r="K82" s="9" t="n"/>
-      <c r="L82" s="9" t="n"/>
-      <c r="M82" s="9" t="n"/>
-      <c r="N82" s="9" t="n"/>
-      <c r="O82" s="9" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="n"/>
-      <c r="B83" s="10" t="n"/>
-      <c r="C83" s="9" t="n"/>
-      <c r="D83" s="9" t="n"/>
-      <c r="E83" s="9" t="n"/>
-      <c r="F83" s="9" t="n"/>
-      <c r="G83" s="9" t="n"/>
-      <c r="H83" s="9" t="n"/>
-      <c r="I83" s="9" t="n"/>
-      <c r="J83" s="9" t="n"/>
-      <c r="K83" s="9" t="n"/>
-      <c r="L83" s="9" t="n"/>
-      <c r="M83" s="9" t="n"/>
-      <c r="N83" s="9" t="n"/>
-      <c r="O83" s="9" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="8" t="n"/>
-      <c r="B84" s="10" t="n"/>
-      <c r="C84" s="9" t="n"/>
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="9" t="n"/>
-      <c r="F84" s="9" t="n"/>
-      <c r="G84" s="9" t="n"/>
-      <c r="H84" s="9" t="n"/>
-      <c r="I84" s="9" t="n"/>
-      <c r="J84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
-      <c r="L84" s="9" t="n"/>
-      <c r="M84" s="9" t="n"/>
-      <c r="N84" s="9" t="n"/>
-      <c r="O84" s="9" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="n"/>
-      <c r="B85" s="10" t="n"/>
-      <c r="C85" s="9" t="n"/>
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="9" t="n"/>
-      <c r="F85" s="9" t="n"/>
-      <c r="G85" s="9" t="n"/>
-      <c r="H85" s="9" t="n"/>
-      <c r="I85" s="9" t="n"/>
-      <c r="J85" s="9" t="n"/>
-      <c r="K85" s="9" t="n"/>
-      <c r="L85" s="9" t="n"/>
-      <c r="M85" s="9" t="n"/>
-      <c r="N85" s="9" t="n"/>
-      <c r="O85" s="9" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="n"/>
-      <c r="B86" s="10" t="n"/>
-      <c r="C86" s="9" t="n"/>
-      <c r="D86" s="9" t="n"/>
-      <c r="E86" s="9" t="n"/>
-      <c r="F86" s="9" t="n"/>
-      <c r="G86" s="9" t="n"/>
-      <c r="H86" s="9" t="n"/>
-      <c r="I86" s="9" t="n"/>
-      <c r="J86" s="9" t="n"/>
-      <c r="K86" s="9" t="n"/>
-      <c r="L86" s="9" t="n"/>
-      <c r="M86" s="9" t="n"/>
-      <c r="N86" s="9" t="n"/>
-      <c r="O86" s="9" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="n"/>
-      <c r="B87" s="10" t="n"/>
-      <c r="C87" s="9" t="n"/>
-      <c r="D87" s="9" t="n"/>
-      <c r="E87" s="9" t="n"/>
-      <c r="F87" s="9" t="n"/>
-      <c r="G87" s="9" t="n"/>
-      <c r="H87" s="9" t="n"/>
-      <c r="I87" s="9" t="n"/>
-      <c r="J87" s="9" t="n"/>
-      <c r="K87" s="9" t="n"/>
-      <c r="L87" s="9" t="n"/>
-      <c r="M87" s="9" t="n"/>
-      <c r="N87" s="9" t="n"/>
-      <c r="O87" s="9" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="n"/>
-      <c r="B88" s="10" t="n"/>
-      <c r="C88" s="9" t="n"/>
-      <c r="D88" s="9" t="n"/>
-      <c r="E88" s="9" t="n"/>
-      <c r="F88" s="9" t="n"/>
-      <c r="G88" s="9" t="n"/>
-      <c r="H88" s="9" t="n"/>
-      <c r="I88" s="9" t="n"/>
-      <c r="J88" s="9" t="n"/>
-      <c r="K88" s="9" t="n"/>
-      <c r="L88" s="9" t="n"/>
-      <c r="M88" s="9" t="n"/>
-      <c r="N88" s="9" t="n"/>
-      <c r="O88" s="9" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="8" t="n"/>
-      <c r="B89" s="10" t="n"/>
-      <c r="C89" s="9" t="n"/>
-      <c r="D89" s="9" t="n"/>
-      <c r="E89" s="9" t="n"/>
-      <c r="F89" s="9" t="n"/>
-      <c r="G89" s="9" t="n"/>
-      <c r="H89" s="9" t="n"/>
-      <c r="I89" s="9" t="n"/>
-      <c r="J89" s="9" t="n"/>
-      <c r="K89" s="9" t="n"/>
-      <c r="L89" s="9" t="n"/>
-      <c r="M89" s="9" t="n"/>
-      <c r="N89" s="9" t="n"/>
-      <c r="O89" s="9" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="n"/>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="9" t="n"/>
-      <c r="E90" s="9" t="n"/>
-      <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
-      <c r="H90" s="9" t="n"/>
-      <c r="I90" s="9" t="n"/>
-      <c r="J90" s="9" t="n"/>
-      <c r="K90" s="9" t="n"/>
-      <c r="L90" s="9" t="n"/>
-      <c r="M90" s="9" t="n"/>
-      <c r="N90" s="9" t="n"/>
-      <c r="O90" s="9" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="8" t="n"/>
-      <c r="B91" s="10" t="n"/>
-      <c r="C91" s="9" t="n"/>
-      <c r="D91" s="9" t="n"/>
-      <c r="E91" s="9" t="n"/>
-      <c r="F91" s="9" t="n"/>
-      <c r="G91" s="9" t="n"/>
-      <c r="H91" s="9" t="n"/>
-      <c r="I91" s="9" t="n"/>
-      <c r="J91" s="9" t="n"/>
-      <c r="K91" s="9" t="n"/>
-      <c r="L91" s="9" t="n"/>
-      <c r="M91" s="9" t="n"/>
-      <c r="N91" s="9" t="n"/>
-      <c r="O91" s="9" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="8" t="n"/>
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="9" t="n"/>
-      <c r="D92" s="9" t="n"/>
-      <c r="E92" s="9" t="n"/>
-      <c r="F92" s="9" t="n"/>
-      <c r="G92" s="9" t="n"/>
-      <c r="H92" s="9" t="n"/>
-      <c r="I92" s="9" t="n"/>
-      <c r="J92" s="9" t="n"/>
-      <c r="K92" s="9" t="n"/>
-      <c r="L92" s="9" t="n"/>
-      <c r="M92" s="9" t="n"/>
-      <c r="N92" s="9" t="n"/>
-      <c r="O92" s="9" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="8" t="n"/>
-      <c r="B93" s="10" t="n"/>
-      <c r="C93" s="9" t="n"/>
-      <c r="D93" s="9" t="n"/>
-      <c r="E93" s="9" t="n"/>
-      <c r="F93" s="9" t="n"/>
-      <c r="G93" s="9" t="n"/>
-      <c r="H93" s="9" t="n"/>
-      <c r="I93" s="9" t="n"/>
-      <c r="J93" s="9" t="n"/>
-      <c r="K93" s="9" t="n"/>
-      <c r="L93" s="9" t="n"/>
-      <c r="M93" s="9" t="n"/>
-      <c r="N93" s="9" t="n"/>
-      <c r="O93" s="9" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="8" t="n"/>
-      <c r="B94" s="10" t="n"/>
-      <c r="C94" s="9" t="n"/>
-      <c r="D94" s="9" t="n"/>
-      <c r="E94" s="9" t="n"/>
-      <c r="F94" s="9" t="n"/>
-      <c r="G94" s="9" t="n"/>
-      <c r="H94" s="9" t="n"/>
-      <c r="I94" s="9" t="n"/>
-      <c r="J94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
-      <c r="L94" s="9" t="n"/>
-      <c r="M94" s="9" t="n"/>
-      <c r="N94" s="9" t="n"/>
-      <c r="O94" s="9" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="8" t="n"/>
-      <c r="B95" s="10" t="n"/>
-      <c r="C95" s="9" t="n"/>
-      <c r="D95" s="9" t="n"/>
-      <c r="E95" s="9" t="n"/>
-      <c r="F95" s="9" t="n"/>
-      <c r="G95" s="9" t="n"/>
-      <c r="H95" s="9" t="n"/>
-      <c r="I95" s="9" t="n"/>
-      <c r="J95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
-      <c r="L95" s="9" t="n"/>
-      <c r="M95" s="9" t="n"/>
-      <c r="N95" s="9" t="n"/>
-      <c r="O95" s="9" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="n"/>
-      <c r="B96" s="10" t="n"/>
-      <c r="C96" s="9" t="n"/>
-      <c r="D96" s="9" t="n"/>
-      <c r="E96" s="9" t="n"/>
-      <c r="F96" s="9" t="n"/>
-      <c r="G96" s="9" t="n"/>
-      <c r="H96" s="9" t="n"/>
-      <c r="I96" s="9" t="n"/>
-      <c r="J96" s="9" t="n"/>
-      <c r="K96" s="9" t="n"/>
-      <c r="L96" s="9" t="n"/>
-      <c r="M96" s="9" t="n"/>
-      <c r="N96" s="9" t="n"/>
-      <c r="O96" s="9" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="n"/>
-      <c r="B97" s="10" t="n"/>
-      <c r="C97" s="9" t="n"/>
-      <c r="D97" s="9" t="n"/>
-      <c r="E97" s="9" t="n"/>
-      <c r="F97" s="9" t="n"/>
-      <c r="G97" s="9" t="n"/>
-      <c r="H97" s="9" t="n"/>
-      <c r="I97" s="9" t="n"/>
-      <c r="J97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
-      <c r="L97" s="9" t="n"/>
-      <c r="M97" s="9" t="n"/>
-      <c r="N97" s="9" t="n"/>
-      <c r="O97" s="9" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="8" t="n"/>
-      <c r="B98" s="10" t="n"/>
-      <c r="C98" s="9" t="n"/>
-      <c r="D98" s="9" t="n"/>
-      <c r="E98" s="9" t="n"/>
-      <c r="F98" s="9" t="n"/>
-      <c r="G98" s="9" t="n"/>
-      <c r="H98" s="9" t="n"/>
-      <c r="I98" s="9" t="n"/>
-      <c r="J98" s="9" t="n"/>
-      <c r="K98" s="9" t="n"/>
-      <c r="L98" s="9" t="n"/>
-      <c r="M98" s="9" t="n"/>
-      <c r="N98" s="9" t="n"/>
-      <c r="O98" s="9" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="n"/>
-      <c r="B99" s="10" t="n"/>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
-      <c r="E99" s="9" t="n"/>
-      <c r="F99" s="9" t="n"/>
-      <c r="G99" s="9" t="n"/>
-      <c r="H99" s="9" t="n"/>
-      <c r="I99" s="9" t="n"/>
-      <c r="J99" s="9" t="n"/>
-      <c r="K99" s="9" t="n"/>
-      <c r="L99" s="9" t="n"/>
-      <c r="M99" s="9" t="n"/>
-      <c r="N99" s="9" t="n"/>
-      <c r="O99" s="9" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="8" t="n"/>
-      <c r="B100" s="10" t="n"/>
-      <c r="C100" s="9" t="n"/>
-      <c r="D100" s="9" t="n"/>
-      <c r="E100" s="9" t="n"/>
-      <c r="F100" s="9" t="n"/>
-      <c r="G100" s="9" t="n"/>
-      <c r="H100" s="9" t="n"/>
-      <c r="I100" s="9" t="n"/>
-      <c r="J100" s="9" t="n"/>
-      <c r="K100" s="9" t="n"/>
-      <c r="L100" s="9" t="n"/>
-      <c r="M100" s="9" t="n"/>
-      <c r="N100" s="9" t="n"/>
-      <c r="O100" s="9" t="n"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="12" t="n"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="12" t="n"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="12" t="n"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="12" t="n"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="12" t="n"/>
-    </row>
-    <row r="106">
-      <c r="B106" s="12" t="n"/>
-    </row>
-    <row r="107">
-      <c r="B107" s="12" t="n"/>
-    </row>
-    <row r="108">
-      <c r="B108" s="12" t="n"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="12" t="n"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="12" t="n"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="12" t="n"/>
-    </row>
-    <row r="112">
-      <c r="B112" s="12" t="n"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="12" t="n"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="12" t="n"/>
-    </row>
-    <row r="115">
-      <c r="B115" s="12" t="n"/>
-    </row>
-    <row r="116">
-      <c r="B116" s="12" t="n"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="12" t="n"/>
-    </row>
-    <row r="118">
-      <c r="B118" s="12" t="n"/>
-    </row>
-    <row r="119">
-      <c r="B119" s="12" t="n"/>
-    </row>
-    <row r="120">
-      <c r="B120" s="12" t="n"/>
-    </row>
-    <row r="121">
-      <c r="B121" s="12" t="n"/>
-    </row>
-    <row r="122">
-      <c r="B122" s="12" t="n"/>
-    </row>
-    <row r="123">
-      <c r="B123" s="12" t="n"/>
-    </row>
-    <row r="124">
-      <c r="B124" s="12" t="n"/>
-    </row>
-    <row r="125">
-      <c r="B125" s="12" t="n"/>
-    </row>
-    <row r="126">
-      <c r="B126" s="12" t="n"/>
-    </row>
-    <row r="127">
-      <c r="B127" s="12" t="n"/>
-    </row>
-    <row r="128">
-      <c r="B128" s="12" t="n"/>
-    </row>
-    <row r="129">
-      <c r="B129" s="12" t="n"/>
-    </row>
-    <row r="130">
-      <c r="B130" s="12" t="n"/>
-    </row>
-    <row r="131">
-      <c r="B131" s="12" t="n"/>
-    </row>
-    <row r="132">
-      <c r="B132" s="12" t="n"/>
-    </row>
-    <row r="133">
-      <c r="B133" s="12" t="n"/>
-    </row>
-    <row r="134">
-      <c r="B134" s="12" t="n"/>
-    </row>
-    <row r="135">
-      <c r="B135" s="12" t="n"/>
-    </row>
-    <row r="136">
-      <c r="B136" s="12" t="n"/>
-    </row>
-    <row r="137">
-      <c r="B137" s="12" t="n"/>
-    </row>
-    <row r="138">
-      <c r="B138" s="12" t="n"/>
-    </row>
-    <row r="139">
-      <c r="B139" s="12" t="n"/>
-    </row>
-    <row r="140">
-      <c r="B140" s="12" t="n"/>
-    </row>
-    <row r="141">
-      <c r="B141" s="12" t="n"/>
-    </row>
-    <row r="142">
-      <c r="B142" s="12" t="n"/>
-    </row>
-    <row r="143">
-      <c r="B143" s="12" t="n"/>
-    </row>
-    <row r="144">
-      <c r="B144" s="12" t="n"/>
-    </row>
-    <row r="145">
-      <c r="B145" s="12" t="n"/>
-    </row>
-    <row r="146">
-      <c r="B146" s="12" t="n"/>
-    </row>
-    <row r="147">
-      <c r="B147" s="12" t="n"/>
-    </row>
-    <row r="148">
-      <c r="B148" s="12" t="n"/>
-    </row>
-    <row r="149">
-      <c r="B149" s="12" t="n"/>
-    </row>
-    <row r="150">
-      <c r="B150" s="12" t="n"/>
-    </row>
-    <row r="151">
-      <c r="B151" s="12" t="n"/>
-    </row>
-    <row r="152">
-      <c r="B152" s="12" t="n"/>
-    </row>
-    <row r="153">
-      <c r="B153" s="12" t="n"/>
-    </row>
-    <row r="154">
-      <c r="B154" s="12" t="n"/>
-    </row>
-    <row r="155">
-      <c r="B155" s="12" t="n"/>
-    </row>
-    <row r="156">
-      <c r="B156" s="12" t="n"/>
-    </row>
-    <row r="157">
-      <c r="B157" s="12" t="n"/>
-    </row>
-    <row r="158">
-      <c r="B158" s="12" t="n"/>
-    </row>
-    <row r="159">
-      <c r="B159" s="12" t="n"/>
-    </row>
-    <row r="160">
-      <c r="B160" s="12" t="n"/>
-    </row>
-    <row r="161">
-      <c r="B161" s="12" t="n"/>
-    </row>
-    <row r="162">
-      <c r="B162" s="12" t="n"/>
-    </row>
-    <row r="163">
-      <c r="B163" s="12" t="n"/>
-    </row>
-    <row r="164">
-      <c r="B164" s="12" t="n"/>
-    </row>
-    <row r="165">
-      <c r="B165" s="12" t="n"/>
-    </row>
-    <row r="166">
-      <c r="B166" s="12" t="n"/>
-    </row>
-    <row r="167">
-      <c r="B167" s="12" t="n"/>
-    </row>
-    <row r="168">
-      <c r="B168" s="12" t="n"/>
-    </row>
-    <row r="169">
-      <c r="B169" s="12" t="n"/>
-    </row>
-    <row r="170">
-      <c r="B170" s="12" t="n"/>
-    </row>
-    <row r="171">
-      <c r="B171" s="12" t="n"/>
-    </row>
-    <row r="172">
-      <c r="B172" s="12" t="n"/>
-    </row>
-    <row r="173">
-      <c r="B173" s="12" t="n"/>
-    </row>
-    <row r="174">
-      <c r="B174" s="12" t="n"/>
-    </row>
-    <row r="175">
-      <c r="B175" s="12" t="n"/>
-    </row>
-    <row r="176">
-      <c r="B176" s="12" t="n"/>
-    </row>
-    <row r="177">
-      <c r="B177" s="12" t="n"/>
-    </row>
-    <row r="178">
-      <c r="B178" s="12" t="n"/>
-    </row>
-    <row r="179">
-      <c r="B179" s="12" t="n"/>
-    </row>
-    <row r="180">
-      <c r="B180" s="12" t="n"/>
-    </row>
-    <row r="181">
-      <c r="B181" s="12" t="n"/>
-    </row>
-    <row r="182">
-      <c r="B182" s="12" t="n"/>
-    </row>
-    <row r="183">
-      <c r="B183" s="12" t="n"/>
-    </row>
-    <row r="184">
-      <c r="B184" s="12" t="n"/>
-    </row>
-    <row r="185">
-      <c r="B185" s="12" t="n"/>
-    </row>
-    <row r="186">
-      <c r="B186" s="12" t="n"/>
-    </row>
-    <row r="187">
-      <c r="B187" s="12" t="n"/>
-    </row>
-    <row r="188">
-      <c r="B188" s="12" t="n"/>
-    </row>
-    <row r="189">
-      <c r="B189" s="12" t="n"/>
-    </row>
-    <row r="190">
-      <c r="B190" s="12" t="n"/>
-    </row>
-    <row r="191">
-      <c r="B191" s="12" t="n"/>
-    </row>
-    <row r="192">
-      <c r="B192" s="12" t="n"/>
-    </row>
-    <row r="193">
-      <c r="B193" s="12" t="n"/>
-    </row>
-    <row r="194">
-      <c r="B194" s="12" t="n"/>
-    </row>
-    <row r="195">
-      <c r="B195" s="12" t="n"/>
-    </row>
-    <row r="196">
-      <c r="B196" s="12" t="n"/>
-    </row>
-    <row r="197">
-      <c r="B197" s="12" t="n"/>
-    </row>
-    <row r="198">
-      <c r="B198" s="12" t="n"/>
-    </row>
-    <row r="199">
-      <c r="B199" s="12" t="n"/>
-    </row>
-    <row r="200">
-      <c r="B200" s="12" t="n"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="วันที่ไม่ถูกต้อง" error="ต้องเป็นวันที่ ค.ศ (ปี 2020–2035) เช่น 15/06/2026 — ถ้าพิมพ์ พ.ศ (เช่น 2569) จะไม่ผ่าน" promptTitle="รูปแบบวันที่ (ค.ศ)" prompt="กรอก วว/ดด/ปปปป (ค.ศ) เช่น 15/06/2026  •  ห้ามใช้ พ.ศ" type="date" operator="between">
-      <formula1>DATE(2020,1,1)</formula1>
-      <formula2>DATE(2035,12,31)</formula2>
-    </dataValidation>
-    <dataValidation sqref="O3:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"paint,wood,hardware,other"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/WAYTHAI-FORYOU_Template.xlsx
+++ b/WAYTHAI-FORYOU_Template.xlsx
@@ -285,6 +285,13 @@
         <t>ค่าสีและวัสดุทุกชนิด บันทึกที่ชีตนี้
 เลือก category = paint / wood / hardware / labor
 (ไม่มีชีต material แยกแล้ว)</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>ซื้อเชื่อ: ใส่จำนวนวันเครดิต (30/45/60)
+จ่ายเงินสดทันที: ใส่ 0
+ระบบใช้คำนวณ AP/เจ้าหนี้ + DPO</t>
       </text>
     </comment>
   </commentList>
@@ -692,7 +699,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr"/>
     </row>
@@ -3077,7 +3083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3085,6 +3091,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3113,6 +3121,16 @@
           <t>รายการ/หมายเหตุ (เช่น ร้านที่ซื้อ/แบรนด์สี)</t>
         </is>
       </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>เครดิตเทอม (วัน)  — เงินสดใส่ 0</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>ประเภท (คงที่/ผันแปร)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -3138,6 +3156,16 @@
       <c r="E2" s="7" t="inlineStr">
         <is>
           <t>note</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>credit_term</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>expense_kind</t>
         </is>
       </c>
     </row>
@@ -4128,13 +4156,19 @@
       <c r="B200" s="12" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="วันที่ไม่ถูกต้อง" error="ต้องเป็นวันที่ ค.ศ (ปี 2020–2035) เช่น 15/06/2026 — ถ้าพิมพ์ พ.ศ (เช่น 2569) จะไม่ผ่าน" promptTitle="รูปแบบวันที่ (ค.ศ)" prompt="กรอก วว/ดด/ปปปป (ค.ศ) เช่น 15/06/2026  •  ห้ามใช้ พ.ศ" type="date" operator="between">
       <formula1>DATE(2020,1,1)</formula1>
       <formula2>DATE(2035,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="C3:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"paint,wood,hardware,labor,marketing,ads,rent,utility,overhead,other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="ประเภทค่าใช้จ่าย" prompt="fixed = คงที่ (เช่า/เงินเดือน) | variable = ผันแปร (วัสดุ/ค่าสี)" type="list">
+      <formula1>"fixed,variable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="เครดิตเทอม (วัน)" prompt="ซื้อเชื่อกี่วัน เช่น 30/45/60 — ถ้าจ่ายเงินสดทันทีใส่ 0" type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
